--- a/DPS PILKADES 2026/RW 10.xlsx
+++ b/DPS PILKADES 2026/RW 10.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PILKADES 2026 NEW\DPS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PILKADES 2026 NEW\DPS PILKADES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C718D9C9-4902-447F-9EC6-F4CEC937AC33}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F767999-3401-4DBF-AEA7-1057738F8FD0}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{446934D1-4919-CD42-A8AE-295386199D19}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10594" uniqueCount="1891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10674" uniqueCount="1941">
   <si>
     <t>NO</t>
   </si>
@@ -5716,13 +5716,163 @@
   </si>
   <si>
     <t>DESA GENTAN KECAMATAN BAKI TAHUN 2026</t>
+  </si>
+  <si>
+    <t>3311100303080003</t>
+  </si>
+  <si>
+    <t>3311105002090002</t>
+  </si>
+  <si>
+    <t>3311102006560001</t>
+  </si>
+  <si>
+    <t>3374095901090002</t>
+  </si>
+  <si>
+    <t>3311101810090001</t>
+  </si>
+  <si>
+    <t>3311106203930003</t>
+  </si>
+  <si>
+    <t>3311106504730002</t>
+  </si>
+  <si>
+    <t>3311101405057804</t>
+  </si>
+  <si>
+    <t>3311101104090001</t>
+  </si>
+  <si>
+    <t>3311101509090003</t>
+  </si>
+  <si>
+    <t>3311101509090002</t>
+  </si>
+  <si>
+    <t>3311100602080001</t>
+  </si>
+  <si>
+    <t>3311101310080001</t>
+  </si>
+  <si>
+    <t>3311100308770004</t>
+  </si>
+  <si>
+    <t>3311105812080001</t>
+  </si>
+  <si>
+    <t>3372017105080001</t>
+  </si>
+  <si>
+    <t>3311106406080003</t>
+  </si>
+  <si>
+    <t>3314025311080002</t>
+  </si>
+  <si>
+    <t>3311107105080003</t>
+  </si>
+  <si>
+    <t>3311102501030005</t>
+  </si>
+  <si>
+    <t>3311102411740003</t>
+  </si>
+  <si>
+    <t>3311083101090001</t>
+  </si>
+  <si>
+    <t>3309142108830004</t>
+  </si>
+  <si>
+    <t>3309141201090002</t>
+  </si>
+  <si>
+    <t>3311102302670004</t>
+  </si>
+  <si>
+    <t>3311103105870001</t>
+  </si>
+  <si>
+    <t>3374030605130012</t>
+  </si>
+  <si>
+    <t>6207045302880001</t>
+  </si>
+  <si>
+    <t>3301210710050002</t>
+  </si>
+  <si>
+    <t>3301213110170003</t>
+  </si>
+  <si>
+    <t>3301215804070006</t>
+  </si>
+  <si>
+    <t>3372011905940003</t>
+  </si>
+  <si>
+    <t>3471116906900001</t>
+  </si>
+  <si>
+    <t>3311100309240001</t>
+  </si>
+  <si>
+    <t>3172061606940002</t>
+  </si>
+  <si>
+    <t>3311102602260003</t>
+  </si>
+  <si>
+    <t>3372016810970007</t>
+  </si>
+  <si>
+    <t>3311100107250001</t>
+  </si>
+  <si>
+    <t>3311100811240003</t>
+  </si>
+  <si>
+    <t>3310054411990005</t>
+  </si>
+  <si>
+    <t>3311121505054975</t>
+  </si>
+  <si>
+    <t>3311126808580001</t>
+  </si>
+  <si>
+    <t>3311106810600001</t>
+  </si>
+  <si>
+    <t>3172041708690001</t>
+  </si>
+  <si>
+    <t>3312120503710002</t>
+  </si>
+  <si>
+    <t>3311122809570001</t>
+  </si>
+  <si>
+    <t>3311123007820007</t>
+  </si>
+  <si>
+    <t>3311125305850002</t>
+  </si>
+  <si>
+    <t>3577025610950001</t>
+  </si>
+  <si>
+    <t>3311102404240004</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -5768,6 +5918,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -6153,7 +6309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6365,6 +6521,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6715,7 +6904,7 @@
     <col min="11" max="11" width="14.6328125" customWidth="1"/>
     <col min="12" max="18" width="3.6328125" customWidth="1"/>
     <col min="19" max="19" width="2.6328125" customWidth="1"/>
-    <col min="21" max="22" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="17.36328125" style="82" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:22" ht="24.6">
@@ -6828,10 +7017,10 @@
       <c r="P6" s="56"/>
       <c r="Q6" s="56"/>
       <c r="R6" s="57"/>
-      <c r="U6" s="12" t="s">
+      <c r="U6" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="V6" s="12" t="s">
+      <c r="V6" s="74" t="s">
         <v>1205</v>
       </c>
     </row>
@@ -6878,10 +7067,10 @@
       <c r="P7" s="53"/>
       <c r="Q7" s="53"/>
       <c r="R7" s="54"/>
-      <c r="U7" s="58">
+      <c r="U7" s="75">
         <v>6</v>
       </c>
-      <c r="V7" s="60">
+      <c r="V7" s="76">
         <v>7</v>
       </c>
     </row>
@@ -6918,8 +7107,8 @@
       <c r="R8" s="38">
         <v>7</v>
       </c>
-      <c r="U8" s="59"/>
-      <c r="V8" s="61"/>
+      <c r="U8" s="77"/>
+      <c r="V8" s="78"/>
     </row>
     <row r="9" spans="1:22" ht="30" customHeight="1">
       <c r="A9" s="43">
@@ -6960,10 +7149,10 @@
       <c r="P9" s="42"/>
       <c r="Q9" s="42"/>
       <c r="R9" s="42"/>
-      <c r="U9" s="9" t="s">
+      <c r="U9" s="79" t="s">
         <v>1206</v>
       </c>
-      <c r="V9" s="9" t="s">
+      <c r="V9" s="79" t="s">
         <v>1207</v>
       </c>
     </row>
@@ -7007,10 +7196,10 @@
       <c r="P10" s="40"/>
       <c r="Q10" s="40"/>
       <c r="R10" s="40"/>
-      <c r="U10" s="9" t="s">
+      <c r="U10" s="79" t="s">
         <v>1208</v>
       </c>
-      <c r="V10" s="9" t="s">
+      <c r="V10" s="79" t="s">
         <v>1209</v>
       </c>
     </row>
@@ -7054,10 +7243,10 @@
       <c r="P11" s="40"/>
       <c r="Q11" s="40"/>
       <c r="R11" s="40"/>
-      <c r="U11" s="9" t="s">
+      <c r="U11" s="79" t="s">
         <v>1210</v>
       </c>
-      <c r="V11" s="9" t="s">
+      <c r="V11" s="79" t="s">
         <v>1209</v>
       </c>
     </row>
@@ -7101,10 +7290,10 @@
       <c r="P12" s="40"/>
       <c r="Q12" s="40"/>
       <c r="R12" s="40"/>
-      <c r="U12" s="9" t="s">
+      <c r="U12" s="79" t="s">
         <v>1211</v>
       </c>
-      <c r="V12" s="9" t="s">
+      <c r="V12" s="79" t="s">
         <v>1209</v>
       </c>
     </row>
@@ -7148,10 +7337,10 @@
       <c r="P13" s="40"/>
       <c r="Q13" s="40"/>
       <c r="R13" s="40"/>
-      <c r="U13" s="9" t="s">
+      <c r="U13" s="79" t="s">
         <v>1212</v>
       </c>
-      <c r="V13" s="9" t="s">
+      <c r="V13" s="79" t="s">
         <v>1213</v>
       </c>
     </row>
@@ -7195,10 +7384,10 @@
       <c r="P14" s="40"/>
       <c r="Q14" s="40"/>
       <c r="R14" s="40"/>
-      <c r="U14" s="9" t="s">
+      <c r="U14" s="79" t="s">
         <v>1214</v>
       </c>
-      <c r="V14" s="9" t="s">
+      <c r="V14" s="79" t="s">
         <v>1213</v>
       </c>
     </row>
@@ -7242,10 +7431,10 @@
       <c r="P15" s="40"/>
       <c r="Q15" s="40"/>
       <c r="R15" s="40"/>
-      <c r="U15" s="9" t="s">
+      <c r="U15" s="79" t="s">
         <v>1215</v>
       </c>
-      <c r="V15" s="9" t="s">
+      <c r="V15" s="79" t="s">
         <v>1216</v>
       </c>
     </row>
@@ -7289,10 +7478,10 @@
       <c r="P16" s="40"/>
       <c r="Q16" s="40"/>
       <c r="R16" s="40"/>
-      <c r="U16" s="9" t="s">
+      <c r="U16" s="79" t="s">
         <v>1217</v>
       </c>
-      <c r="V16" s="9" t="s">
+      <c r="V16" s="79" t="s">
         <v>1216</v>
       </c>
     </row>
@@ -7336,10 +7525,10 @@
       <c r="P17" s="40"/>
       <c r="Q17" s="40"/>
       <c r="R17" s="40"/>
-      <c r="U17" s="9" t="s">
+      <c r="U17" s="79" t="s">
         <v>1218</v>
       </c>
-      <c r="V17" s="9" t="s">
+      <c r="V17" s="79" t="s">
         <v>1219</v>
       </c>
     </row>
@@ -7383,10 +7572,10 @@
       <c r="P18" s="40"/>
       <c r="Q18" s="40"/>
       <c r="R18" s="40"/>
-      <c r="U18" s="9" t="s">
+      <c r="U18" s="79" t="s">
         <v>1220</v>
       </c>
-      <c r="V18" s="9" t="s">
+      <c r="V18" s="79" t="s">
         <v>1221</v>
       </c>
     </row>
@@ -7430,10 +7619,10 @@
       <c r="P19" s="40"/>
       <c r="Q19" s="40"/>
       <c r="R19" s="40"/>
-      <c r="U19" s="9" t="s">
+      <c r="U19" s="79" t="s">
         <v>1222</v>
       </c>
-      <c r="V19" s="9" t="s">
+      <c r="V19" s="79" t="s">
         <v>1223</v>
       </c>
     </row>
@@ -7477,10 +7666,10 @@
       <c r="P20" s="40"/>
       <c r="Q20" s="40"/>
       <c r="R20" s="40"/>
-      <c r="U20" s="9" t="s">
+      <c r="U20" s="79" t="s">
         <v>1224</v>
       </c>
-      <c r="V20" s="9" t="s">
+      <c r="V20" s="79" t="s">
         <v>1223</v>
       </c>
     </row>
@@ -7524,10 +7713,10 @@
       <c r="P21" s="40"/>
       <c r="Q21" s="40"/>
       <c r="R21" s="40"/>
-      <c r="U21" s="9" t="s">
+      <c r="U21" s="79" t="s">
         <v>1225</v>
       </c>
-      <c r="V21" s="9" t="s">
+      <c r="V21" s="79" t="s">
         <v>1223</v>
       </c>
     </row>
@@ -7571,10 +7760,10 @@
       <c r="P22" s="40"/>
       <c r="Q22" s="40"/>
       <c r="R22" s="40"/>
-      <c r="U22" s="9" t="s">
+      <c r="U22" s="79" t="s">
         <v>1226</v>
       </c>
-      <c r="V22" s="9" t="s">
+      <c r="V22" s="79" t="s">
         <v>1227</v>
       </c>
     </row>
@@ -7618,10 +7807,10 @@
       <c r="P23" s="40"/>
       <c r="Q23" s="40"/>
       <c r="R23" s="40"/>
-      <c r="U23" s="9" t="s">
+      <c r="U23" s="79" t="s">
         <v>1228</v>
       </c>
-      <c r="V23" s="9" t="s">
+      <c r="V23" s="79" t="s">
         <v>1227</v>
       </c>
     </row>
@@ -7665,10 +7854,10 @@
       <c r="P24" s="40"/>
       <c r="Q24" s="40"/>
       <c r="R24" s="40"/>
-      <c r="U24" s="9" t="s">
+      <c r="U24" s="79" t="s">
         <v>1229</v>
       </c>
-      <c r="V24" s="9" t="s">
+      <c r="V24" s="79" t="s">
         <v>1230</v>
       </c>
     </row>
@@ -7712,10 +7901,10 @@
       <c r="P25" s="40"/>
       <c r="Q25" s="40"/>
       <c r="R25" s="40"/>
-      <c r="U25" s="9" t="s">
+      <c r="U25" s="79" t="s">
         <v>1231</v>
       </c>
-      <c r="V25" s="9" t="s">
+      <c r="V25" s="79" t="s">
         <v>1230</v>
       </c>
     </row>
@@ -7759,10 +7948,10 @@
       <c r="P26" s="40"/>
       <c r="Q26" s="40"/>
       <c r="R26" s="40"/>
-      <c r="U26" s="9" t="s">
+      <c r="U26" s="79" t="s">
         <v>1232</v>
       </c>
-      <c r="V26" s="9" t="s">
+      <c r="V26" s="79" t="s">
         <v>1233</v>
       </c>
     </row>
@@ -7806,10 +7995,10 @@
       <c r="P27" s="40"/>
       <c r="Q27" s="40"/>
       <c r="R27" s="40"/>
-      <c r="U27" s="9" t="s">
+      <c r="U27" s="79" t="s">
         <v>1234</v>
       </c>
-      <c r="V27" s="9" t="s">
+      <c r="V27" s="79" t="s">
         <v>1235</v>
       </c>
     </row>
@@ -7853,10 +8042,10 @@
       <c r="P28" s="40"/>
       <c r="Q28" s="40"/>
       <c r="R28" s="40"/>
-      <c r="U28" s="9" t="s">
+      <c r="U28" s="79" t="s">
         <v>1236</v>
       </c>
-      <c r="V28" s="9" t="s">
+      <c r="V28" s="79" t="s">
         <v>1235</v>
       </c>
     </row>
@@ -7900,10 +8089,10 @@
       <c r="P29" s="40"/>
       <c r="Q29" s="40"/>
       <c r="R29" s="40"/>
-      <c r="U29" s="9" t="s">
+      <c r="U29" s="79" t="s">
         <v>1237</v>
       </c>
-      <c r="V29" s="9" t="s">
+      <c r="V29" s="79" t="s">
         <v>1238</v>
       </c>
     </row>
@@ -7947,10 +8136,10 @@
       <c r="P30" s="40"/>
       <c r="Q30" s="40"/>
       <c r="R30" s="40"/>
-      <c r="U30" s="9" t="s">
+      <c r="U30" s="79" t="s">
         <v>1239</v>
       </c>
-      <c r="V30" s="9" t="s">
+      <c r="V30" s="79" t="s">
         <v>1238</v>
       </c>
     </row>
@@ -7994,10 +8183,10 @@
       <c r="P31" s="40"/>
       <c r="Q31" s="40"/>
       <c r="R31" s="40"/>
-      <c r="U31" s="9" t="s">
+      <c r="U31" s="79" t="s">
         <v>1240</v>
       </c>
-      <c r="V31" s="9" t="s">
+      <c r="V31" s="79" t="s">
         <v>1241</v>
       </c>
     </row>
@@ -8041,10 +8230,10 @@
       <c r="P32" s="40"/>
       <c r="Q32" s="40"/>
       <c r="R32" s="40"/>
-      <c r="U32" s="9" t="s">
+      <c r="U32" s="79" t="s">
         <v>1242</v>
       </c>
-      <c r="V32" s="9" t="s">
+      <c r="V32" s="79" t="s">
         <v>1241</v>
       </c>
     </row>
@@ -8088,10 +8277,10 @@
       <c r="P33" s="40"/>
       <c r="Q33" s="40"/>
       <c r="R33" s="40"/>
-      <c r="U33" s="9" t="s">
+      <c r="U33" s="79" t="s">
         <v>1243</v>
       </c>
-      <c r="V33" s="9" t="s">
+      <c r="V33" s="79" t="s">
         <v>1244</v>
       </c>
     </row>
@@ -8135,10 +8324,10 @@
       <c r="P34" s="40"/>
       <c r="Q34" s="40"/>
       <c r="R34" s="40"/>
-      <c r="U34" s="9" t="s">
+      <c r="U34" s="79" t="s">
         <v>1245</v>
       </c>
-      <c r="V34" s="9" t="s">
+      <c r="V34" s="79" t="s">
         <v>1244</v>
       </c>
     </row>
@@ -8182,10 +8371,10 @@
       <c r="P35" s="40"/>
       <c r="Q35" s="40"/>
       <c r="R35" s="40"/>
-      <c r="U35" s="9" t="s">
+      <c r="U35" s="79" t="s">
         <v>1246</v>
       </c>
-      <c r="V35" s="9" t="s">
+      <c r="V35" s="79" t="s">
         <v>1247</v>
       </c>
     </row>
@@ -8229,10 +8418,10 @@
       <c r="P36" s="40"/>
       <c r="Q36" s="40"/>
       <c r="R36" s="40"/>
-      <c r="U36" s="9" t="s">
+      <c r="U36" s="79" t="s">
         <v>1248</v>
       </c>
-      <c r="V36" s="9" t="s">
+      <c r="V36" s="79" t="s">
         <v>1249</v>
       </c>
     </row>
@@ -8276,10 +8465,10 @@
       <c r="P37" s="40"/>
       <c r="Q37" s="40"/>
       <c r="R37" s="40"/>
-      <c r="U37" s="9" t="s">
+      <c r="U37" s="79" t="s">
         <v>1250</v>
       </c>
-      <c r="V37" s="9" t="s">
+      <c r="V37" s="79" t="s">
         <v>1249</v>
       </c>
     </row>
@@ -8323,10 +8512,10 @@
       <c r="P38" s="40"/>
       <c r="Q38" s="40"/>
       <c r="R38" s="40"/>
-      <c r="U38" s="9" t="s">
+      <c r="U38" s="79" t="s">
         <v>1251</v>
       </c>
-      <c r="V38" s="9" t="s">
+      <c r="V38" s="79" t="s">
         <v>1249</v>
       </c>
     </row>
@@ -8370,10 +8559,10 @@
       <c r="P39" s="40"/>
       <c r="Q39" s="40"/>
       <c r="R39" s="40"/>
-      <c r="U39" s="9" t="s">
+      <c r="U39" s="79" t="s">
         <v>1252</v>
       </c>
-      <c r="V39" s="9" t="s">
+      <c r="V39" s="79" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -8417,10 +8606,10 @@
       <c r="P40" s="40"/>
       <c r="Q40" s="40"/>
       <c r="R40" s="40"/>
-      <c r="U40" s="9" t="s">
+      <c r="U40" s="79" t="s">
         <v>1254</v>
       </c>
-      <c r="V40" s="9" t="s">
+      <c r="V40" s="79" t="s">
         <v>1253</v>
       </c>
     </row>
@@ -8464,10 +8653,10 @@
       <c r="P41" s="40"/>
       <c r="Q41" s="40"/>
       <c r="R41" s="40"/>
-      <c r="U41" s="9" t="s">
+      <c r="U41" s="79" t="s">
         <v>1255</v>
       </c>
-      <c r="V41" s="9" t="s">
+      <c r="V41" s="79" t="s">
         <v>1256</v>
       </c>
     </row>
@@ -8511,10 +8700,10 @@
       <c r="P42" s="40"/>
       <c r="Q42" s="40"/>
       <c r="R42" s="40"/>
-      <c r="U42" s="9" t="s">
+      <c r="U42" s="79" t="s">
         <v>1257</v>
       </c>
-      <c r="V42" s="9" t="s">
+      <c r="V42" s="79" t="s">
         <v>1258</v>
       </c>
     </row>
@@ -8558,10 +8747,10 @@
       <c r="P43" s="40"/>
       <c r="Q43" s="40"/>
       <c r="R43" s="40"/>
-      <c r="U43" s="9" t="s">
+      <c r="U43" s="79" t="s">
         <v>1259</v>
       </c>
-      <c r="V43" s="9" t="s">
+      <c r="V43" s="79" t="s">
         <v>1258</v>
       </c>
     </row>
@@ -8605,10 +8794,10 @@
       <c r="P44" s="40"/>
       <c r="Q44" s="40"/>
       <c r="R44" s="40"/>
-      <c r="U44" s="9" t="s">
+      <c r="U44" s="79" t="s">
         <v>1260</v>
       </c>
-      <c r="V44" s="9" t="s">
+      <c r="V44" s="79" t="s">
         <v>1261</v>
       </c>
     </row>
@@ -8652,10 +8841,10 @@
       <c r="P45" s="40"/>
       <c r="Q45" s="40"/>
       <c r="R45" s="40"/>
-      <c r="U45" s="9" t="s">
+      <c r="U45" s="79" t="s">
         <v>1262</v>
       </c>
-      <c r="V45" s="9" t="s">
+      <c r="V45" s="79" t="s">
         <v>1261</v>
       </c>
     </row>
@@ -8699,10 +8888,10 @@
       <c r="P46" s="40"/>
       <c r="Q46" s="40"/>
       <c r="R46" s="40"/>
-      <c r="U46" s="9" t="s">
+      <c r="U46" s="79" t="s">
         <v>1263</v>
       </c>
-      <c r="V46" s="9" t="s">
+      <c r="V46" s="79" t="s">
         <v>1261</v>
       </c>
     </row>
@@ -8746,10 +8935,10 @@
       <c r="P47" s="40"/>
       <c r="Q47" s="40"/>
       <c r="R47" s="40"/>
-      <c r="U47" s="9" t="s">
+      <c r="U47" s="79" t="s">
         <v>1264</v>
       </c>
-      <c r="V47" s="9" t="s">
+      <c r="V47" s="79" t="s">
         <v>1265</v>
       </c>
     </row>
@@ -8793,10 +8982,10 @@
       <c r="P48" s="40"/>
       <c r="Q48" s="40"/>
       <c r="R48" s="40"/>
-      <c r="U48" s="9" t="s">
+      <c r="U48" s="79" t="s">
         <v>1266</v>
       </c>
-      <c r="V48" s="9" t="s">
+      <c r="V48" s="79" t="s">
         <v>1267</v>
       </c>
     </row>
@@ -8840,10 +9029,10 @@
       <c r="P49" s="40"/>
       <c r="Q49" s="40"/>
       <c r="R49" s="40"/>
-      <c r="U49" s="9" t="s">
+      <c r="U49" s="79" t="s">
         <v>1268</v>
       </c>
-      <c r="V49" s="9" t="s">
+      <c r="V49" s="79" t="s">
         <v>1269</v>
       </c>
     </row>
@@ -8887,10 +9076,10 @@
       <c r="P50" s="40"/>
       <c r="Q50" s="40"/>
       <c r="R50" s="40"/>
-      <c r="U50" s="9" t="s">
+      <c r="U50" s="79" t="s">
         <v>1270</v>
       </c>
-      <c r="V50" s="9" t="s">
+      <c r="V50" s="79" t="s">
         <v>1269</v>
       </c>
     </row>
@@ -8934,10 +9123,10 @@
       <c r="P51" s="40"/>
       <c r="Q51" s="40"/>
       <c r="R51" s="40"/>
-      <c r="U51" s="9" t="s">
+      <c r="U51" s="79" t="s">
         <v>1271</v>
       </c>
-      <c r="V51" s="9" t="s">
+      <c r="V51" s="79" t="s">
         <v>1269</v>
       </c>
     </row>
@@ -8981,10 +9170,10 @@
       <c r="P52" s="40"/>
       <c r="Q52" s="40"/>
       <c r="R52" s="40"/>
-      <c r="U52" s="9" t="s">
+      <c r="U52" s="79" t="s">
         <v>1272</v>
       </c>
-      <c r="V52" s="9" t="s">
+      <c r="V52" s="79" t="s">
         <v>1269</v>
       </c>
     </row>
@@ -9028,10 +9217,10 @@
       <c r="P53" s="40"/>
       <c r="Q53" s="40"/>
       <c r="R53" s="40"/>
-      <c r="U53" s="9" t="s">
+      <c r="U53" s="79" t="s">
         <v>1273</v>
       </c>
-      <c r="V53" s="9" t="s">
+      <c r="V53" s="79" t="s">
         <v>1274</v>
       </c>
     </row>
@@ -9075,10 +9264,10 @@
       <c r="P54" s="40"/>
       <c r="Q54" s="40"/>
       <c r="R54" s="40"/>
-      <c r="U54" s="9" t="s">
+      <c r="U54" s="79" t="s">
         <v>1275</v>
       </c>
-      <c r="V54" s="9" t="s">
+      <c r="V54" s="79" t="s">
         <v>1274</v>
       </c>
     </row>
@@ -9122,10 +9311,10 @@
       <c r="P55" s="40"/>
       <c r="Q55" s="40"/>
       <c r="R55" s="40"/>
-      <c r="U55" s="9" t="s">
+      <c r="U55" s="79" t="s">
         <v>1276</v>
       </c>
-      <c r="V55" s="9" t="s">
+      <c r="V55" s="79" t="s">
         <v>1277</v>
       </c>
     </row>
@@ -9169,10 +9358,10 @@
       <c r="P56" s="40"/>
       <c r="Q56" s="40"/>
       <c r="R56" s="40"/>
-      <c r="U56" s="9" t="s">
+      <c r="U56" s="79" t="s">
         <v>1278</v>
       </c>
-      <c r="V56" s="9" t="s">
+      <c r="V56" s="79" t="s">
         <v>1277</v>
       </c>
     </row>
@@ -9216,10 +9405,10 @@
       <c r="P57" s="40"/>
       <c r="Q57" s="40"/>
       <c r="R57" s="40"/>
-      <c r="U57" s="9" t="s">
+      <c r="U57" s="79" t="s">
         <v>1279</v>
       </c>
-      <c r="V57" s="9" t="s">
+      <c r="V57" s="79" t="s">
         <v>1280</v>
       </c>
     </row>
@@ -9263,10 +9452,10 @@
       <c r="P58" s="40"/>
       <c r="Q58" s="40"/>
       <c r="R58" s="40"/>
-      <c r="U58" s="9" t="s">
+      <c r="U58" s="79" t="s">
         <v>1281</v>
       </c>
-      <c r="V58" s="9" t="s">
+      <c r="V58" s="79" t="s">
         <v>1280</v>
       </c>
     </row>
@@ -9310,10 +9499,10 @@
       <c r="P59" s="40"/>
       <c r="Q59" s="40"/>
       <c r="R59" s="40"/>
-      <c r="U59" s="9" t="s">
+      <c r="U59" s="79" t="s">
         <v>1282</v>
       </c>
-      <c r="V59" s="9" t="s">
+      <c r="V59" s="79" t="s">
         <v>1283</v>
       </c>
     </row>
@@ -9357,10 +9546,10 @@
       <c r="P60" s="40"/>
       <c r="Q60" s="40"/>
       <c r="R60" s="40"/>
-      <c r="U60" s="9" t="s">
+      <c r="U60" s="79" t="s">
         <v>1284</v>
       </c>
-      <c r="V60" s="9" t="s">
+      <c r="V60" s="79" t="s">
         <v>1283</v>
       </c>
     </row>
@@ -9404,10 +9593,10 @@
       <c r="P61" s="40"/>
       <c r="Q61" s="40"/>
       <c r="R61" s="40"/>
-      <c r="U61" s="9" t="s">
+      <c r="U61" s="79" t="s">
         <v>1285</v>
       </c>
-      <c r="V61" s="9" t="s">
+      <c r="V61" s="79" t="s">
         <v>1283</v>
       </c>
     </row>
@@ -9451,10 +9640,10 @@
       <c r="P62" s="40"/>
       <c r="Q62" s="40"/>
       <c r="R62" s="40"/>
-      <c r="U62" s="9" t="s">
+      <c r="U62" s="79" t="s">
         <v>1286</v>
       </c>
-      <c r="V62" s="9" t="s">
+      <c r="V62" s="79" t="s">
         <v>1287</v>
       </c>
     </row>
@@ -9498,10 +9687,10 @@
       <c r="P63" s="40"/>
       <c r="Q63" s="40"/>
       <c r="R63" s="40"/>
-      <c r="U63" s="9" t="s">
+      <c r="U63" s="79" t="s">
         <v>1288</v>
       </c>
-      <c r="V63" s="9" t="s">
+      <c r="V63" s="79" t="s">
         <v>1287</v>
       </c>
     </row>
@@ -9545,10 +9734,10 @@
       <c r="P64" s="40"/>
       <c r="Q64" s="40"/>
       <c r="R64" s="40"/>
-      <c r="U64" s="9" t="s">
+      <c r="U64" s="79" t="s">
         <v>1289</v>
       </c>
-      <c r="V64" s="9" t="s">
+      <c r="V64" s="79" t="s">
         <v>1290</v>
       </c>
     </row>
@@ -9592,10 +9781,10 @@
       <c r="P65" s="40"/>
       <c r="Q65" s="40"/>
       <c r="R65" s="40"/>
-      <c r="U65" s="9" t="s">
+      <c r="U65" s="79" t="s">
         <v>1291</v>
       </c>
-      <c r="V65" s="9" t="s">
+      <c r="V65" s="79" t="s">
         <v>1290</v>
       </c>
     </row>
@@ -9639,10 +9828,10 @@
       <c r="P66" s="40"/>
       <c r="Q66" s="40"/>
       <c r="R66" s="40"/>
-      <c r="U66" s="9" t="s">
+      <c r="U66" s="79" t="s">
         <v>1292</v>
       </c>
-      <c r="V66" s="9" t="s">
+      <c r="V66" s="79" t="s">
         <v>1293</v>
       </c>
     </row>
@@ -9686,10 +9875,10 @@
       <c r="P67" s="40"/>
       <c r="Q67" s="40"/>
       <c r="R67" s="40"/>
-      <c r="U67" s="9" t="s">
+      <c r="U67" s="79" t="s">
         <v>1294</v>
       </c>
-      <c r="V67" s="9" t="s">
+      <c r="V67" s="79" t="s">
         <v>1295</v>
       </c>
     </row>
@@ -9733,10 +9922,10 @@
       <c r="P68" s="40"/>
       <c r="Q68" s="40"/>
       <c r="R68" s="40"/>
-      <c r="U68" s="9" t="s">
+      <c r="U68" s="79" t="s">
         <v>1296</v>
       </c>
-      <c r="V68" s="9" t="s">
+      <c r="V68" s="79" t="s">
         <v>1295</v>
       </c>
     </row>
@@ -9780,10 +9969,10 @@
       <c r="P69" s="40"/>
       <c r="Q69" s="40"/>
       <c r="R69" s="40"/>
-      <c r="U69" s="9" t="s">
+      <c r="U69" s="79" t="s">
         <v>1297</v>
       </c>
-      <c r="V69" s="9" t="s">
+      <c r="V69" s="79" t="s">
         <v>1298</v>
       </c>
     </row>
@@ -9827,10 +10016,10 @@
       <c r="P70" s="40"/>
       <c r="Q70" s="40"/>
       <c r="R70" s="40"/>
-      <c r="U70" s="9" t="s">
+      <c r="U70" s="79" t="s">
         <v>1299</v>
       </c>
-      <c r="V70" s="9" t="s">
+      <c r="V70" s="79" t="s">
         <v>1300</v>
       </c>
     </row>
@@ -9874,10 +10063,10 @@
       <c r="P71" s="40"/>
       <c r="Q71" s="40"/>
       <c r="R71" s="40"/>
-      <c r="U71" s="9" t="s">
+      <c r="U71" s="79" t="s">
         <v>1301</v>
       </c>
-      <c r="V71" s="9" t="s">
+      <c r="V71" s="79" t="s">
         <v>1302</v>
       </c>
     </row>
@@ -9921,10 +10110,10 @@
       <c r="P72" s="40"/>
       <c r="Q72" s="40"/>
       <c r="R72" s="40"/>
-      <c r="U72" s="9" t="s">
+      <c r="U72" s="79" t="s">
         <v>1303</v>
       </c>
-      <c r="V72" s="9" t="s">
+      <c r="V72" s="79" t="s">
         <v>1302</v>
       </c>
     </row>
@@ -9968,10 +10157,10 @@
       <c r="P73" s="40"/>
       <c r="Q73" s="40"/>
       <c r="R73" s="40"/>
-      <c r="U73" s="9" t="s">
+      <c r="U73" s="79" t="s">
         <v>1304</v>
       </c>
-      <c r="V73" s="9" t="s">
+      <c r="V73" s="79" t="s">
         <v>1305</v>
       </c>
     </row>
@@ -10015,10 +10204,10 @@
       <c r="P74" s="40"/>
       <c r="Q74" s="40"/>
       <c r="R74" s="40"/>
-      <c r="U74" s="9" t="s">
+      <c r="U74" s="79" t="s">
         <v>1306</v>
       </c>
-      <c r="V74" s="9" t="s">
+      <c r="V74" s="79" t="s">
         <v>1305</v>
       </c>
     </row>
@@ -10062,10 +10251,10 @@
       <c r="P75" s="40"/>
       <c r="Q75" s="40"/>
       <c r="R75" s="40"/>
-      <c r="U75" s="9" t="s">
+      <c r="U75" s="79" t="s">
         <v>1307</v>
       </c>
-      <c r="V75" s="9" t="s">
+      <c r="V75" s="79" t="s">
         <v>1308</v>
       </c>
     </row>
@@ -10109,10 +10298,10 @@
       <c r="P76" s="40"/>
       <c r="Q76" s="40"/>
       <c r="R76" s="40"/>
-      <c r="U76" s="9" t="s">
+      <c r="U76" s="79" t="s">
         <v>1309</v>
       </c>
-      <c r="V76" s="9" t="s">
+      <c r="V76" s="79" t="s">
         <v>1308</v>
       </c>
     </row>
@@ -10156,10 +10345,10 @@
       <c r="P77" s="40"/>
       <c r="Q77" s="40"/>
       <c r="R77" s="40"/>
-      <c r="U77" s="9" t="s">
+      <c r="U77" s="79" t="s">
         <v>1310</v>
       </c>
-      <c r="V77" s="9" t="s">
+      <c r="V77" s="79" t="s">
         <v>1308</v>
       </c>
     </row>
@@ -10206,8 +10395,12 @@
       <c r="S78" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U78" s="10"/>
-      <c r="V78" s="10"/>
+      <c r="U78" s="80" t="s">
+        <v>1913</v>
+      </c>
+      <c r="V78" s="80" t="s">
+        <v>1914</v>
+      </c>
     </row>
     <row r="79" spans="1:22" ht="30" customHeight="1">
       <c r="A79" s="43" t="s">
@@ -10252,8 +10445,12 @@
       <c r="S79" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U79" s="10"/>
-      <c r="V79" s="10"/>
+      <c r="U79" s="83" t="s">
+        <v>1891</v>
+      </c>
+      <c r="V79" s="83" t="s">
+        <v>1209</v>
+      </c>
     </row>
     <row r="80" spans="1:22" ht="30" customHeight="1">
       <c r="A80" s="43" t="s">
@@ -10298,8 +10495,12 @@
       <c r="S80" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U80" s="10"/>
-      <c r="V80" s="10"/>
+      <c r="U80" s="83" t="s">
+        <v>1892</v>
+      </c>
+      <c r="V80" s="83" t="s">
+        <v>1233</v>
+      </c>
     </row>
     <row r="81" spans="1:22" ht="30" customHeight="1">
       <c r="A81" s="43" t="s">
@@ -10344,8 +10545,12 @@
       <c r="S81" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U81" s="10"/>
-      <c r="V81" s="10"/>
+      <c r="U81" s="80" t="s">
+        <v>1915</v>
+      </c>
+      <c r="V81" s="80" t="s">
+        <v>1235</v>
+      </c>
     </row>
     <row r="82" spans="1:22" ht="30" customHeight="1">
       <c r="A82" s="43" t="s">
@@ -10390,8 +10595,12 @@
       <c r="S82" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U82" s="10"/>
-      <c r="V82" s="10"/>
+      <c r="U82" s="83" t="s">
+        <v>1893</v>
+      </c>
+      <c r="V82" s="83" t="s">
+        <v>1247</v>
+      </c>
     </row>
     <row r="83" spans="1:22" ht="30" customHeight="1">
       <c r="A83" s="43" t="s">
@@ -10436,8 +10645,12 @@
       <c r="S83" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U83" s="10"/>
-      <c r="V83" s="10"/>
+      <c r="U83" s="83" t="s">
+        <v>1894</v>
+      </c>
+      <c r="V83" s="83" t="s">
+        <v>1269</v>
+      </c>
     </row>
     <row r="84" spans="1:22" ht="30" customHeight="1">
       <c r="A84" s="43" t="s">
@@ -10482,8 +10695,12 @@
       <c r="S84" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U84" s="10"/>
-      <c r="V84" s="10"/>
+      <c r="U84" s="83" t="s">
+        <v>1895</v>
+      </c>
+      <c r="V84" s="83" t="s">
+        <v>1280</v>
+      </c>
     </row>
     <row r="85" spans="1:22" ht="30" customHeight="1">
       <c r="A85" s="43" t="s">
@@ -10528,8 +10745,12 @@
       <c r="S85" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U85" s="10"/>
-      <c r="V85" s="10"/>
+      <c r="U85" s="80" t="s">
+        <v>1916</v>
+      </c>
+      <c r="V85" s="80" t="s">
+        <v>1917</v>
+      </c>
     </row>
     <row r="86" spans="1:22" ht="30" customHeight="1">
       <c r="A86" s="43" t="s">
@@ -10574,8 +10795,12 @@
       <c r="S86" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U86" s="10"/>
-      <c r="V86" s="10"/>
+      <c r="U86" s="80" t="s">
+        <v>1918</v>
+      </c>
+      <c r="V86" s="80" t="s">
+        <v>1917</v>
+      </c>
     </row>
     <row r="87" spans="1:22" ht="15" customHeight="1">
       <c r="A87" s="43"/>
@@ -10597,8 +10822,8 @@
       <c r="Q87" s="40"/>
       <c r="R87" s="40"/>
       <c r="S87" s="39"/>
-      <c r="U87" s="10"/>
-      <c r="V87" s="10"/>
+      <c r="U87" s="81"/>
+      <c r="V87" s="81"/>
     </row>
     <row r="88" spans="1:22" ht="30" customHeight="1">
       <c r="A88" s="43" t="s">
@@ -10639,10 +10864,10 @@
       <c r="P88" s="40"/>
       <c r="Q88" s="40"/>
       <c r="R88" s="40"/>
-      <c r="U88" s="9" t="s">
+      <c r="U88" s="79" t="s">
         <v>1311</v>
       </c>
-      <c r="V88" s="9" t="s">
+      <c r="V88" s="79" t="s">
         <v>1312</v>
       </c>
     </row>
@@ -10686,10 +10911,10 @@
       <c r="P89" s="40"/>
       <c r="Q89" s="40"/>
       <c r="R89" s="40"/>
-      <c r="U89" s="9" t="s">
+      <c r="U89" s="79" t="s">
         <v>1313</v>
       </c>
-      <c r="V89" s="9" t="s">
+      <c r="V89" s="79" t="s">
         <v>1312</v>
       </c>
     </row>
@@ -10733,10 +10958,10 @@
       <c r="P90" s="40"/>
       <c r="Q90" s="40"/>
       <c r="R90" s="40"/>
-      <c r="U90" s="9" t="s">
+      <c r="U90" s="79" t="s">
         <v>1314</v>
       </c>
-      <c r="V90" s="9" t="s">
+      <c r="V90" s="79" t="s">
         <v>1315</v>
       </c>
     </row>
@@ -10780,10 +11005,10 @@
       <c r="P91" s="40"/>
       <c r="Q91" s="40"/>
       <c r="R91" s="40"/>
-      <c r="U91" s="9" t="s">
+      <c r="U91" s="79" t="s">
         <v>1316</v>
       </c>
-      <c r="V91" s="9" t="s">
+      <c r="V91" s="79" t="s">
         <v>1315</v>
       </c>
     </row>
@@ -10827,10 +11052,10 @@
       <c r="P92" s="40"/>
       <c r="Q92" s="40"/>
       <c r="R92" s="40"/>
-      <c r="U92" s="9" t="s">
+      <c r="U92" s="79" t="s">
         <v>1317</v>
       </c>
-      <c r="V92" s="9" t="s">
+      <c r="V92" s="79" t="s">
         <v>1318</v>
       </c>
     </row>
@@ -10874,10 +11099,10 @@
       <c r="P93" s="40"/>
       <c r="Q93" s="40"/>
       <c r="R93" s="40"/>
-      <c r="U93" s="9" t="s">
+      <c r="U93" s="79" t="s">
         <v>1319</v>
       </c>
-      <c r="V93" s="9" t="s">
+      <c r="V93" s="79" t="s">
         <v>1320</v>
       </c>
     </row>
@@ -10921,10 +11146,10 @@
       <c r="P94" s="40"/>
       <c r="Q94" s="40"/>
       <c r="R94" s="40"/>
-      <c r="U94" s="9" t="s">
+      <c r="U94" s="79" t="s">
         <v>1321</v>
       </c>
-      <c r="V94" s="9" t="s">
+      <c r="V94" s="79" t="s">
         <v>1320</v>
       </c>
     </row>
@@ -10968,10 +11193,10 @@
       <c r="P95" s="40"/>
       <c r="Q95" s="40"/>
       <c r="R95" s="40"/>
-      <c r="U95" s="9" t="s">
+      <c r="U95" s="79" t="s">
         <v>1322</v>
       </c>
-      <c r="V95" s="9" t="s">
+      <c r="V95" s="79" t="s">
         <v>1320</v>
       </c>
     </row>
@@ -11015,10 +11240,10 @@
       <c r="P96" s="40"/>
       <c r="Q96" s="40"/>
       <c r="R96" s="40"/>
-      <c r="U96" s="9" t="s">
+      <c r="U96" s="79" t="s">
         <v>1323</v>
       </c>
-      <c r="V96" s="9" t="s">
+      <c r="V96" s="79" t="s">
         <v>1320</v>
       </c>
     </row>
@@ -11062,10 +11287,10 @@
       <c r="P97" s="40"/>
       <c r="Q97" s="40"/>
       <c r="R97" s="40"/>
-      <c r="U97" s="9" t="s">
+      <c r="U97" s="79" t="s">
         <v>1324</v>
       </c>
-      <c r="V97" s="9" t="s">
+      <c r="V97" s="79" t="s">
         <v>1325</v>
       </c>
     </row>
@@ -11109,10 +11334,10 @@
       <c r="P98" s="40"/>
       <c r="Q98" s="40"/>
       <c r="R98" s="40"/>
-      <c r="U98" s="9" t="s">
+      <c r="U98" s="79" t="s">
         <v>1326</v>
       </c>
-      <c r="V98" s="9" t="s">
+      <c r="V98" s="79" t="s">
         <v>1327</v>
       </c>
     </row>
@@ -11156,10 +11381,10 @@
       <c r="P99" s="40"/>
       <c r="Q99" s="40"/>
       <c r="R99" s="40"/>
-      <c r="U99" s="9" t="s">
+      <c r="U99" s="79" t="s">
         <v>1328</v>
       </c>
-      <c r="V99" s="9" t="s">
+      <c r="V99" s="79" t="s">
         <v>1327</v>
       </c>
     </row>
@@ -11203,10 +11428,10 @@
       <c r="P100" s="40"/>
       <c r="Q100" s="40"/>
       <c r="R100" s="40"/>
-      <c r="U100" s="9" t="s">
+      <c r="U100" s="79" t="s">
         <v>1329</v>
       </c>
-      <c r="V100" s="9" t="s">
+      <c r="V100" s="79" t="s">
         <v>1330</v>
       </c>
     </row>
@@ -11250,10 +11475,10 @@
       <c r="P101" s="40"/>
       <c r="Q101" s="40"/>
       <c r="R101" s="40"/>
-      <c r="U101" s="9" t="s">
+      <c r="U101" s="79" t="s">
         <v>1331</v>
       </c>
-      <c r="V101" s="9" t="s">
+      <c r="V101" s="79" t="s">
         <v>1330</v>
       </c>
     </row>
@@ -11297,10 +11522,10 @@
       <c r="P102" s="40"/>
       <c r="Q102" s="40"/>
       <c r="R102" s="40"/>
-      <c r="U102" s="9" t="s">
+      <c r="U102" s="79" t="s">
         <v>1332</v>
       </c>
-      <c r="V102" s="9" t="s">
+      <c r="V102" s="79" t="s">
         <v>1333</v>
       </c>
     </row>
@@ -11344,10 +11569,10 @@
       <c r="P103" s="40"/>
       <c r="Q103" s="40"/>
       <c r="R103" s="40"/>
-      <c r="U103" s="9" t="s">
+      <c r="U103" s="79" t="s">
         <v>1334</v>
       </c>
-      <c r="V103" s="9" t="s">
+      <c r="V103" s="79" t="s">
         <v>1333</v>
       </c>
     </row>
@@ -11391,10 +11616,10 @@
       <c r="P104" s="40"/>
       <c r="Q104" s="40"/>
       <c r="R104" s="40"/>
-      <c r="U104" s="9" t="s">
+      <c r="U104" s="79" t="s">
         <v>1335</v>
       </c>
-      <c r="V104" s="9" t="s">
+      <c r="V104" s="79" t="s">
         <v>1336</v>
       </c>
     </row>
@@ -11438,10 +11663,10 @@
       <c r="P105" s="40"/>
       <c r="Q105" s="40"/>
       <c r="R105" s="40"/>
-      <c r="U105" s="9" t="s">
+      <c r="U105" s="79" t="s">
         <v>1337</v>
       </c>
-      <c r="V105" s="9" t="s">
+      <c r="V105" s="79" t="s">
         <v>1336</v>
       </c>
     </row>
@@ -11485,10 +11710,10 @@
       <c r="P106" s="40"/>
       <c r="Q106" s="40"/>
       <c r="R106" s="40"/>
-      <c r="U106" s="9" t="s">
+      <c r="U106" s="79" t="s">
         <v>1338</v>
       </c>
-      <c r="V106" s="9" t="s">
+      <c r="V106" s="79" t="s">
         <v>1339</v>
       </c>
     </row>
@@ -11532,10 +11757,10 @@
       <c r="P107" s="40"/>
       <c r="Q107" s="40"/>
       <c r="R107" s="40"/>
-      <c r="U107" s="9" t="s">
+      <c r="U107" s="79" t="s">
         <v>1340</v>
       </c>
-      <c r="V107" s="9" t="s">
+      <c r="V107" s="79" t="s">
         <v>1339</v>
       </c>
     </row>
@@ -11579,10 +11804,10 @@
       <c r="P108" s="40"/>
       <c r="Q108" s="40"/>
       <c r="R108" s="40"/>
-      <c r="U108" s="9" t="s">
+      <c r="U108" s="79" t="s">
         <v>1341</v>
       </c>
-      <c r="V108" s="9" t="s">
+      <c r="V108" s="79" t="s">
         <v>1342</v>
       </c>
     </row>
@@ -11626,10 +11851,10 @@
       <c r="P109" s="40"/>
       <c r="Q109" s="40"/>
       <c r="R109" s="40"/>
-      <c r="U109" s="9" t="s">
+      <c r="U109" s="79" t="s">
         <v>1343</v>
       </c>
-      <c r="V109" s="9" t="s">
+      <c r="V109" s="79" t="s">
         <v>1342</v>
       </c>
     </row>
@@ -11673,10 +11898,10 @@
       <c r="P110" s="40"/>
       <c r="Q110" s="40"/>
       <c r="R110" s="40"/>
-      <c r="U110" s="9" t="s">
+      <c r="U110" s="79" t="s">
         <v>1344</v>
       </c>
-      <c r="V110" s="9" t="s">
+      <c r="V110" s="79" t="s">
         <v>1342</v>
       </c>
     </row>
@@ -11720,10 +11945,10 @@
       <c r="P111" s="40"/>
       <c r="Q111" s="40"/>
       <c r="R111" s="40"/>
-      <c r="U111" s="9" t="s">
+      <c r="U111" s="79" t="s">
         <v>1345</v>
       </c>
-      <c r="V111" s="9" t="s">
+      <c r="V111" s="79" t="s">
         <v>1346</v>
       </c>
     </row>
@@ -11767,10 +11992,10 @@
       <c r="P112" s="40"/>
       <c r="Q112" s="40"/>
       <c r="R112" s="40"/>
-      <c r="U112" s="9" t="s">
+      <c r="U112" s="79" t="s">
         <v>1347</v>
       </c>
-      <c r="V112" s="9" t="s">
+      <c r="V112" s="79" t="s">
         <v>1346</v>
       </c>
     </row>
@@ -11814,10 +12039,10 @@
       <c r="P113" s="40"/>
       <c r="Q113" s="40"/>
       <c r="R113" s="40"/>
-      <c r="U113" s="9" t="s">
+      <c r="U113" s="79" t="s">
         <v>1348</v>
       </c>
-      <c r="V113" s="9" t="s">
+      <c r="V113" s="79" t="s">
         <v>1346</v>
       </c>
     </row>
@@ -11861,10 +12086,10 @@
       <c r="P114" s="40"/>
       <c r="Q114" s="40"/>
       <c r="R114" s="40"/>
-      <c r="U114" s="9" t="s">
+      <c r="U114" s="79" t="s">
         <v>1349</v>
       </c>
-      <c r="V114" s="9" t="s">
+      <c r="V114" s="79" t="s">
         <v>1346</v>
       </c>
     </row>
@@ -11908,10 +12133,10 @@
       <c r="P115" s="40"/>
       <c r="Q115" s="40"/>
       <c r="R115" s="40"/>
-      <c r="U115" s="9" t="s">
+      <c r="U115" s="79" t="s">
         <v>1350</v>
       </c>
-      <c r="V115" s="9" t="s">
+      <c r="V115" s="79" t="s">
         <v>1351</v>
       </c>
     </row>
@@ -11955,10 +12180,10 @@
       <c r="P116" s="40"/>
       <c r="Q116" s="40"/>
       <c r="R116" s="40"/>
-      <c r="U116" s="9" t="s">
+      <c r="U116" s="79" t="s">
         <v>1352</v>
       </c>
-      <c r="V116" s="9" t="s">
+      <c r="V116" s="79" t="s">
         <v>1351</v>
       </c>
     </row>
@@ -12002,10 +12227,10 @@
       <c r="P117" s="40"/>
       <c r="Q117" s="40"/>
       <c r="R117" s="40"/>
-      <c r="U117" s="9" t="s">
+      <c r="U117" s="79" t="s">
         <v>1353</v>
       </c>
-      <c r="V117" s="9" t="s">
+      <c r="V117" s="79" t="s">
         <v>1351</v>
       </c>
     </row>
@@ -12049,10 +12274,10 @@
       <c r="P118" s="40"/>
       <c r="Q118" s="40"/>
       <c r="R118" s="40"/>
-      <c r="U118" s="9" t="s">
+      <c r="U118" s="79" t="s">
         <v>1354</v>
       </c>
-      <c r="V118" s="9" t="s">
+      <c r="V118" s="79" t="s">
         <v>1355</v>
       </c>
     </row>
@@ -12096,10 +12321,10 @@
       <c r="P119" s="40"/>
       <c r="Q119" s="40"/>
       <c r="R119" s="40"/>
-      <c r="U119" s="9" t="s">
+      <c r="U119" s="79" t="s">
         <v>1356</v>
       </c>
-      <c r="V119" s="9" t="s">
+      <c r="V119" s="79" t="s">
         <v>1355</v>
       </c>
     </row>
@@ -12143,10 +12368,10 @@
       <c r="P120" s="40"/>
       <c r="Q120" s="40"/>
       <c r="R120" s="40"/>
-      <c r="U120" s="9" t="s">
+      <c r="U120" s="79" t="s">
         <v>1357</v>
       </c>
-      <c r="V120" s="9" t="s">
+      <c r="V120" s="79" t="s">
         <v>1358</v>
       </c>
     </row>
@@ -12190,10 +12415,10 @@
       <c r="P121" s="40"/>
       <c r="Q121" s="40"/>
       <c r="R121" s="40"/>
-      <c r="U121" s="9" t="s">
+      <c r="U121" s="79" t="s">
         <v>1359</v>
       </c>
-      <c r="V121" s="9" t="s">
+      <c r="V121" s="79" t="s">
         <v>1358</v>
       </c>
     </row>
@@ -12237,10 +12462,10 @@
       <c r="P122" s="40"/>
       <c r="Q122" s="40"/>
       <c r="R122" s="40"/>
-      <c r="U122" s="9" t="s">
+      <c r="U122" s="79" t="s">
         <v>1360</v>
       </c>
-      <c r="V122" s="9" t="s">
+      <c r="V122" s="79" t="s">
         <v>1358</v>
       </c>
     </row>
@@ -12284,10 +12509,10 @@
       <c r="P123" s="40"/>
       <c r="Q123" s="40"/>
       <c r="R123" s="40"/>
-      <c r="U123" s="9" t="s">
+      <c r="U123" s="79" t="s">
         <v>1361</v>
       </c>
-      <c r="V123" s="9" t="s">
+      <c r="V123" s="79" t="s">
         <v>1362</v>
       </c>
     </row>
@@ -12331,10 +12556,10 @@
       <c r="P124" s="40"/>
       <c r="Q124" s="40"/>
       <c r="R124" s="40"/>
-      <c r="U124" s="9" t="s">
+      <c r="U124" s="79" t="s">
         <v>1363</v>
       </c>
-      <c r="V124" s="9" t="s">
+      <c r="V124" s="79" t="s">
         <v>1362</v>
       </c>
     </row>
@@ -12378,10 +12603,10 @@
       <c r="P125" s="40"/>
       <c r="Q125" s="40"/>
       <c r="R125" s="40"/>
-      <c r="U125" s="9" t="s">
+      <c r="U125" s="79" t="s">
         <v>1364</v>
       </c>
-      <c r="V125" s="9" t="s">
+      <c r="V125" s="79" t="s">
         <v>1362</v>
       </c>
     </row>
@@ -12425,10 +12650,10 @@
       <c r="P126" s="40"/>
       <c r="Q126" s="40"/>
       <c r="R126" s="40"/>
-      <c r="U126" s="9" t="s">
+      <c r="U126" s="79" t="s">
         <v>1365</v>
       </c>
-      <c r="V126" s="9" t="s">
+      <c r="V126" s="79" t="s">
         <v>1366</v>
       </c>
     </row>
@@ -12472,10 +12697,10 @@
       <c r="P127" s="40"/>
       <c r="Q127" s="40"/>
       <c r="R127" s="40"/>
-      <c r="U127" s="9" t="s">
+      <c r="U127" s="79" t="s">
         <v>1367</v>
       </c>
-      <c r="V127" s="9" t="s">
+      <c r="V127" s="79" t="s">
         <v>1368</v>
       </c>
     </row>
@@ -12519,10 +12744,10 @@
       <c r="P128" s="40"/>
       <c r="Q128" s="40"/>
       <c r="R128" s="40"/>
-      <c r="U128" s="9" t="s">
+      <c r="U128" s="79" t="s">
         <v>1369</v>
       </c>
-      <c r="V128" s="9" t="s">
+      <c r="V128" s="79" t="s">
         <v>1370</v>
       </c>
     </row>
@@ -12566,10 +12791,10 @@
       <c r="P129" s="40"/>
       <c r="Q129" s="40"/>
       <c r="R129" s="40"/>
-      <c r="U129" s="9" t="s">
+      <c r="U129" s="79" t="s">
         <v>1371</v>
       </c>
-      <c r="V129" s="9" t="s">
+      <c r="V129" s="79" t="s">
         <v>1370</v>
       </c>
     </row>
@@ -12613,10 +12838,10 @@
       <c r="P130" s="40"/>
       <c r="Q130" s="40"/>
       <c r="R130" s="40"/>
-      <c r="U130" s="9" t="s">
+      <c r="U130" s="79" t="s">
         <v>1372</v>
       </c>
-      <c r="V130" s="9" t="s">
+      <c r="V130" s="79" t="s">
         <v>1370</v>
       </c>
     </row>
@@ -12660,10 +12885,10 @@
       <c r="P131" s="40"/>
       <c r="Q131" s="40"/>
       <c r="R131" s="40"/>
-      <c r="U131" s="9" t="s">
+      <c r="U131" s="79" t="s">
         <v>1373</v>
       </c>
-      <c r="V131" s="9" t="s">
+      <c r="V131" s="79" t="s">
         <v>1368</v>
       </c>
     </row>
@@ -12707,10 +12932,10 @@
       <c r="P132" s="40"/>
       <c r="Q132" s="40"/>
       <c r="R132" s="40"/>
-      <c r="U132" s="9" t="s">
+      <c r="U132" s="79" t="s">
         <v>1374</v>
       </c>
-      <c r="V132" s="9" t="s">
+      <c r="V132" s="79" t="s">
         <v>1368</v>
       </c>
     </row>
@@ -12754,10 +12979,10 @@
       <c r="P133" s="40"/>
       <c r="Q133" s="40"/>
       <c r="R133" s="40"/>
-      <c r="U133" s="9" t="s">
+      <c r="U133" s="79" t="s">
         <v>1375</v>
       </c>
-      <c r="V133" s="9" t="s">
+      <c r="V133" s="79" t="s">
         <v>1376</v>
       </c>
     </row>
@@ -12801,10 +13026,10 @@
       <c r="P134" s="40"/>
       <c r="Q134" s="40"/>
       <c r="R134" s="40"/>
-      <c r="U134" s="9" t="s">
+      <c r="U134" s="79" t="s">
         <v>1377</v>
       </c>
-      <c r="V134" s="9" t="s">
+      <c r="V134" s="79" t="s">
         <v>1376</v>
       </c>
     </row>
@@ -12848,10 +13073,10 @@
       <c r="P135" s="40"/>
       <c r="Q135" s="40"/>
       <c r="R135" s="40"/>
-      <c r="U135" s="9" t="s">
+      <c r="U135" s="79" t="s">
         <v>1378</v>
       </c>
-      <c r="V135" s="9" t="s">
+      <c r="V135" s="79" t="s">
         <v>1376</v>
       </c>
     </row>
@@ -12895,10 +13120,10 @@
       <c r="P136" s="40"/>
       <c r="Q136" s="40"/>
       <c r="R136" s="40"/>
-      <c r="U136" s="9" t="s">
+      <c r="U136" s="79" t="s">
         <v>1379</v>
       </c>
-      <c r="V136" s="9" t="s">
+      <c r="V136" s="79" t="s">
         <v>1380</v>
       </c>
     </row>
@@ -12942,10 +13167,10 @@
       <c r="P137" s="40"/>
       <c r="Q137" s="40"/>
       <c r="R137" s="40"/>
-      <c r="U137" s="9" t="s">
+      <c r="U137" s="79" t="s">
         <v>1381</v>
       </c>
-      <c r="V137" s="9" t="s">
+      <c r="V137" s="79" t="s">
         <v>1380</v>
       </c>
     </row>
@@ -12989,10 +13214,10 @@
       <c r="P138" s="40"/>
       <c r="Q138" s="40"/>
       <c r="R138" s="40"/>
-      <c r="U138" s="9" t="s">
+      <c r="U138" s="79" t="s">
         <v>1382</v>
       </c>
-      <c r="V138" s="9" t="s">
+      <c r="V138" s="79" t="s">
         <v>1380</v>
       </c>
     </row>
@@ -13036,10 +13261,10 @@
       <c r="P139" s="40"/>
       <c r="Q139" s="40"/>
       <c r="R139" s="40"/>
-      <c r="U139" s="9" t="s">
+      <c r="U139" s="79" t="s">
         <v>1383</v>
       </c>
-      <c r="V139" s="9" t="s">
+      <c r="V139" s="79" t="s">
         <v>1384</v>
       </c>
     </row>
@@ -13083,10 +13308,10 @@
       <c r="P140" s="40"/>
       <c r="Q140" s="40"/>
       <c r="R140" s="40"/>
-      <c r="U140" s="9" t="s">
+      <c r="U140" s="79" t="s">
         <v>1385</v>
       </c>
-      <c r="V140" s="9" t="s">
+      <c r="V140" s="79" t="s">
         <v>1384</v>
       </c>
     </row>
@@ -13130,10 +13355,10 @@
       <c r="P141" s="40"/>
       <c r="Q141" s="40"/>
       <c r="R141" s="40"/>
-      <c r="U141" s="9" t="s">
+      <c r="U141" s="79" t="s">
         <v>1386</v>
       </c>
-      <c r="V141" s="9" t="s">
+      <c r="V141" s="79" t="s">
         <v>1387</v>
       </c>
     </row>
@@ -13177,10 +13402,10 @@
       <c r="P142" s="40"/>
       <c r="Q142" s="40"/>
       <c r="R142" s="40"/>
-      <c r="U142" s="9" t="s">
+      <c r="U142" s="79" t="s">
         <v>1388</v>
       </c>
-      <c r="V142" s="9" t="s">
+      <c r="V142" s="79" t="s">
         <v>1387</v>
       </c>
     </row>
@@ -13224,10 +13449,10 @@
       <c r="P143" s="40"/>
       <c r="Q143" s="40"/>
       <c r="R143" s="40"/>
-      <c r="U143" s="9" t="s">
+      <c r="U143" s="79" t="s">
         <v>1389</v>
       </c>
-      <c r="V143" s="9" t="s">
+      <c r="V143" s="79" t="s">
         <v>1390</v>
       </c>
     </row>
@@ -13271,10 +13496,10 @@
       <c r="P144" s="40"/>
       <c r="Q144" s="40"/>
       <c r="R144" s="40"/>
-      <c r="U144" s="9" t="s">
+      <c r="U144" s="79" t="s">
         <v>1391</v>
       </c>
-      <c r="V144" s="9" t="s">
+      <c r="V144" s="79" t="s">
         <v>1390</v>
       </c>
     </row>
@@ -13318,10 +13543,10 @@
       <c r="P145" s="40"/>
       <c r="Q145" s="40"/>
       <c r="R145" s="40"/>
-      <c r="U145" s="9" t="s">
+      <c r="U145" s="79" t="s">
         <v>1392</v>
       </c>
-      <c r="V145" s="9" t="s">
+      <c r="V145" s="79" t="s">
         <v>1393</v>
       </c>
     </row>
@@ -13365,10 +13590,10 @@
       <c r="P146" s="40"/>
       <c r="Q146" s="40"/>
       <c r="R146" s="40"/>
-      <c r="U146" s="9" t="s">
+      <c r="U146" s="79" t="s">
         <v>1394</v>
       </c>
-      <c r="V146" s="9" t="s">
+      <c r="V146" s="79" t="s">
         <v>1393</v>
       </c>
     </row>
@@ -13412,10 +13637,10 @@
       <c r="P147" s="40"/>
       <c r="Q147" s="40"/>
       <c r="R147" s="40"/>
-      <c r="U147" s="9" t="s">
+      <c r="U147" s="79" t="s">
         <v>1395</v>
       </c>
-      <c r="V147" s="9" t="s">
+      <c r="V147" s="79" t="s">
         <v>1396</v>
       </c>
     </row>
@@ -13459,10 +13684,10 @@
       <c r="P148" s="40"/>
       <c r="Q148" s="40"/>
       <c r="R148" s="40"/>
-      <c r="U148" s="9" t="s">
+      <c r="U148" s="79" t="s">
         <v>1397</v>
       </c>
-      <c r="V148" s="9" t="s">
+      <c r="V148" s="79" t="s">
         <v>1396</v>
       </c>
     </row>
@@ -13506,10 +13731,10 @@
       <c r="P149" s="40"/>
       <c r="Q149" s="40"/>
       <c r="R149" s="40"/>
-      <c r="U149" s="9" t="s">
+      <c r="U149" s="79" t="s">
         <v>1398</v>
       </c>
-      <c r="V149" s="9" t="s">
+      <c r="V149" s="79" t="s">
         <v>1399</v>
       </c>
     </row>
@@ -13553,10 +13778,10 @@
       <c r="P150" s="40"/>
       <c r="Q150" s="40"/>
       <c r="R150" s="40"/>
-      <c r="U150" s="9" t="s">
+      <c r="U150" s="79" t="s">
         <v>1400</v>
       </c>
-      <c r="V150" s="9" t="s">
+      <c r="V150" s="79" t="s">
         <v>1399</v>
       </c>
     </row>
@@ -13600,10 +13825,10 @@
       <c r="P151" s="40"/>
       <c r="Q151" s="40"/>
       <c r="R151" s="40"/>
-      <c r="U151" s="9" t="s">
+      <c r="U151" s="79" t="s">
         <v>1401</v>
       </c>
-      <c r="V151" s="9" t="s">
+      <c r="V151" s="79" t="s">
         <v>1399</v>
       </c>
     </row>
@@ -13647,10 +13872,10 @@
       <c r="P152" s="40"/>
       <c r="Q152" s="40"/>
       <c r="R152" s="40"/>
-      <c r="U152" s="9" t="s">
+      <c r="U152" s="79" t="s">
         <v>1402</v>
       </c>
-      <c r="V152" s="9" t="s">
+      <c r="V152" s="79" t="s">
         <v>1399</v>
       </c>
     </row>
@@ -13694,10 +13919,10 @@
       <c r="P153" s="40"/>
       <c r="Q153" s="40"/>
       <c r="R153" s="40"/>
-      <c r="U153" s="9" t="s">
+      <c r="U153" s="79" t="s">
         <v>1403</v>
       </c>
-      <c r="V153" s="9" t="s">
+      <c r="V153" s="79" t="s">
         <v>1404</v>
       </c>
     </row>
@@ -13741,10 +13966,10 @@
       <c r="P154" s="40"/>
       <c r="Q154" s="40"/>
       <c r="R154" s="40"/>
-      <c r="U154" s="9" t="s">
+      <c r="U154" s="79" t="s">
         <v>1405</v>
       </c>
-      <c r="V154" s="9" t="s">
+      <c r="V154" s="79" t="s">
         <v>1404</v>
       </c>
     </row>
@@ -13788,10 +14013,10 @@
       <c r="P155" s="40"/>
       <c r="Q155" s="40"/>
       <c r="R155" s="40"/>
-      <c r="U155" s="9" t="s">
+      <c r="U155" s="79" t="s">
         <v>1406</v>
       </c>
-      <c r="V155" s="9" t="s">
+      <c r="V155" s="79" t="s">
         <v>1404</v>
       </c>
     </row>
@@ -13835,10 +14060,10 @@
       <c r="P156" s="40"/>
       <c r="Q156" s="40"/>
       <c r="R156" s="40"/>
-      <c r="U156" s="9" t="s">
+      <c r="U156" s="79" t="s">
         <v>1407</v>
       </c>
-      <c r="V156" s="9" t="s">
+      <c r="V156" s="79" t="s">
         <v>1404</v>
       </c>
     </row>
@@ -13885,8 +14110,12 @@
       <c r="S157" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U157" s="10"/>
-      <c r="V157" s="10"/>
+      <c r="U157" s="80" t="s">
+        <v>1919</v>
+      </c>
+      <c r="V157" s="80" t="s">
+        <v>1920</v>
+      </c>
     </row>
     <row r="158" spans="1:22" ht="30" customHeight="1">
       <c r="A158" s="43" t="s">
@@ -13931,8 +14160,12 @@
       <c r="S158" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U158" s="10"/>
-      <c r="V158" s="10"/>
+      <c r="U158" s="80" t="s">
+        <v>1921</v>
+      </c>
+      <c r="V158" s="80" t="s">
+        <v>1920</v>
+      </c>
     </row>
     <row r="159" spans="1:22" ht="30" customHeight="1">
       <c r="A159" s="43" t="s">
@@ -13977,8 +14210,12 @@
       <c r="S159" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U159" s="10"/>
-      <c r="V159" s="10"/>
+      <c r="U159" s="83" t="s">
+        <v>1896</v>
+      </c>
+      <c r="V159" s="83" t="s">
+        <v>1339</v>
+      </c>
     </row>
     <row r="160" spans="1:22" ht="30" customHeight="1">
       <c r="A160" s="43" t="s">
@@ -14023,8 +14260,12 @@
       <c r="S160" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U160" s="10"/>
-      <c r="V160" s="10"/>
+      <c r="U160" s="83" t="s">
+        <v>1897</v>
+      </c>
+      <c r="V160" s="83" t="s">
+        <v>1898</v>
+      </c>
     </row>
     <row r="161" spans="1:22" ht="30" customHeight="1">
       <c r="A161" s="43" t="s">
@@ -14069,8 +14310,12 @@
       <c r="S161" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U161" s="10"/>
-      <c r="V161" s="10"/>
+      <c r="U161" s="83" t="s">
+        <v>1899</v>
+      </c>
+      <c r="V161" s="83" t="s">
+        <v>1404</v>
+      </c>
     </row>
     <row r="162" spans="1:22" ht="15" customHeight="1">
       <c r="A162" s="43"/>
@@ -14092,8 +14337,8 @@
       <c r="Q162" s="40"/>
       <c r="R162" s="40"/>
       <c r="S162" s="39"/>
-      <c r="U162" s="10"/>
-      <c r="V162" s="10"/>
+      <c r="U162" s="81"/>
+      <c r="V162" s="81"/>
     </row>
     <row r="163" spans="1:22" ht="30" customHeight="1">
       <c r="A163" s="43">
@@ -14134,10 +14379,10 @@
       <c r="P163" s="40"/>
       <c r="Q163" s="40"/>
       <c r="R163" s="40"/>
-      <c r="U163" s="9" t="s">
+      <c r="U163" s="79" t="s">
         <v>1408</v>
       </c>
-      <c r="V163" s="9" t="s">
+      <c r="V163" s="79" t="s">
         <v>1409</v>
       </c>
     </row>
@@ -14181,10 +14426,10 @@
       <c r="P164" s="40"/>
       <c r="Q164" s="40"/>
       <c r="R164" s="40"/>
-      <c r="U164" s="9" t="s">
+      <c r="U164" s="79" t="s">
         <v>1410</v>
       </c>
-      <c r="V164" s="9" t="s">
+      <c r="V164" s="79" t="s">
         <v>1411</v>
       </c>
     </row>
@@ -14228,10 +14473,10 @@
       <c r="P165" s="40"/>
       <c r="Q165" s="40"/>
       <c r="R165" s="40"/>
-      <c r="U165" s="9" t="s">
+      <c r="U165" s="79" t="s">
         <v>1412</v>
       </c>
-      <c r="V165" s="9" t="s">
+      <c r="V165" s="79" t="s">
         <v>1411</v>
       </c>
     </row>
@@ -14275,10 +14520,10 @@
       <c r="P166" s="40"/>
       <c r="Q166" s="40"/>
       <c r="R166" s="40"/>
-      <c r="U166" s="9" t="s">
+      <c r="U166" s="79" t="s">
         <v>1413</v>
       </c>
-      <c r="V166" s="9" t="s">
+      <c r="V166" s="79" t="s">
         <v>1411</v>
       </c>
     </row>
@@ -14322,10 +14567,10 @@
       <c r="P167" s="40"/>
       <c r="Q167" s="40"/>
       <c r="R167" s="40"/>
-      <c r="U167" s="9" t="s">
+      <c r="U167" s="79" t="s">
         <v>1414</v>
       </c>
-      <c r="V167" s="9" t="s">
+      <c r="V167" s="79" t="s">
         <v>1415</v>
       </c>
     </row>
@@ -14369,10 +14614,10 @@
       <c r="P168" s="40"/>
       <c r="Q168" s="40"/>
       <c r="R168" s="40"/>
-      <c r="U168" s="9" t="s">
+      <c r="U168" s="79" t="s">
         <v>1416</v>
       </c>
-      <c r="V168" s="9" t="s">
+      <c r="V168" s="79" t="s">
         <v>1415</v>
       </c>
     </row>
@@ -14416,10 +14661,10 @@
       <c r="P169" s="40"/>
       <c r="Q169" s="40"/>
       <c r="R169" s="40"/>
-      <c r="U169" s="9" t="s">
+      <c r="U169" s="79" t="s">
         <v>1417</v>
       </c>
-      <c r="V169" s="9" t="s">
+      <c r="V169" s="79" t="s">
         <v>1418</v>
       </c>
     </row>
@@ -14463,10 +14708,10 @@
       <c r="P170" s="40"/>
       <c r="Q170" s="40"/>
       <c r="R170" s="40"/>
-      <c r="U170" s="9" t="s">
+      <c r="U170" s="79" t="s">
         <v>1419</v>
       </c>
-      <c r="V170" s="9" t="s">
+      <c r="V170" s="79" t="s">
         <v>1418</v>
       </c>
     </row>
@@ -14510,10 +14755,10 @@
       <c r="P171" s="40"/>
       <c r="Q171" s="40"/>
       <c r="R171" s="40"/>
-      <c r="U171" s="9" t="s">
+      <c r="U171" s="79" t="s">
         <v>1420</v>
       </c>
-      <c r="V171" s="9" t="s">
+      <c r="V171" s="79" t="s">
         <v>1421</v>
       </c>
     </row>
@@ -14557,10 +14802,10 @@
       <c r="P172" s="40"/>
       <c r="Q172" s="40"/>
       <c r="R172" s="40"/>
-      <c r="U172" s="9" t="s">
+      <c r="U172" s="79" t="s">
         <v>1422</v>
       </c>
-      <c r="V172" s="9" t="s">
+      <c r="V172" s="79" t="s">
         <v>1421</v>
       </c>
     </row>
@@ -14604,10 +14849,10 @@
       <c r="P173" s="40"/>
       <c r="Q173" s="40"/>
       <c r="R173" s="40"/>
-      <c r="U173" s="9" t="s">
+      <c r="U173" s="79" t="s">
         <v>1423</v>
       </c>
-      <c r="V173" s="9" t="s">
+      <c r="V173" s="79" t="s">
         <v>1421</v>
       </c>
     </row>
@@ -14651,10 +14896,10 @@
       <c r="P174" s="40"/>
       <c r="Q174" s="40"/>
       <c r="R174" s="40"/>
-      <c r="U174" s="9" t="s">
+      <c r="U174" s="79" t="s">
         <v>1424</v>
       </c>
-      <c r="V174" s="9" t="s">
+      <c r="V174" s="79" t="s">
         <v>1425</v>
       </c>
     </row>
@@ -14698,10 +14943,10 @@
       <c r="P175" s="40"/>
       <c r="Q175" s="40"/>
       <c r="R175" s="40"/>
-      <c r="U175" s="9" t="s">
+      <c r="U175" s="79" t="s">
         <v>1426</v>
       </c>
-      <c r="V175" s="9" t="s">
+      <c r="V175" s="79" t="s">
         <v>1425</v>
       </c>
     </row>
@@ -14745,10 +14990,10 @@
       <c r="P176" s="40"/>
       <c r="Q176" s="40"/>
       <c r="R176" s="40"/>
-      <c r="U176" s="9" t="s">
+      <c r="U176" s="79" t="s">
         <v>1427</v>
       </c>
-      <c r="V176" s="9" t="s">
+      <c r="V176" s="79" t="s">
         <v>1425</v>
       </c>
     </row>
@@ -14792,10 +15037,10 @@
       <c r="P177" s="40"/>
       <c r="Q177" s="40"/>
       <c r="R177" s="40"/>
-      <c r="U177" s="9" t="s">
+      <c r="U177" s="79" t="s">
         <v>1428</v>
       </c>
-      <c r="V177" s="9" t="s">
+      <c r="V177" s="79" t="s">
         <v>1425</v>
       </c>
     </row>
@@ -14839,10 +15084,10 @@
       <c r="P178" s="40"/>
       <c r="Q178" s="40"/>
       <c r="R178" s="40"/>
-      <c r="U178" s="9" t="s">
+      <c r="U178" s="79" t="s">
         <v>1429</v>
       </c>
-      <c r="V178" s="9" t="s">
+      <c r="V178" s="79" t="s">
         <v>1430</v>
       </c>
     </row>
@@ -14886,10 +15131,10 @@
       <c r="P179" s="40"/>
       <c r="Q179" s="40"/>
       <c r="R179" s="40"/>
-      <c r="U179" s="9" t="s">
+      <c r="U179" s="79" t="s">
         <v>1431</v>
       </c>
-      <c r="V179" s="9" t="s">
+      <c r="V179" s="79" t="s">
         <v>1430</v>
       </c>
     </row>
@@ -14933,10 +15178,10 @@
       <c r="P180" s="40"/>
       <c r="Q180" s="40"/>
       <c r="R180" s="40"/>
-      <c r="U180" s="9" t="s">
+      <c r="U180" s="79" t="s">
         <v>1432</v>
       </c>
-      <c r="V180" s="9" t="s">
+      <c r="V180" s="79" t="s">
         <v>1433</v>
       </c>
     </row>
@@ -14980,10 +15225,10 @@
       <c r="P181" s="40"/>
       <c r="Q181" s="40"/>
       <c r="R181" s="40"/>
-      <c r="U181" s="9" t="s">
+      <c r="U181" s="79" t="s">
         <v>1434</v>
       </c>
-      <c r="V181" s="9" t="s">
+      <c r="V181" s="79" t="s">
         <v>1433</v>
       </c>
     </row>
@@ -15027,10 +15272,10 @@
       <c r="P182" s="40"/>
       <c r="Q182" s="40"/>
       <c r="R182" s="40"/>
-      <c r="U182" s="9" t="s">
+      <c r="U182" s="79" t="s">
         <v>1435</v>
       </c>
-      <c r="V182" s="9" t="s">
+      <c r="V182" s="79" t="s">
         <v>1436</v>
       </c>
     </row>
@@ -15074,10 +15319,10 @@
       <c r="P183" s="40"/>
       <c r="Q183" s="40"/>
       <c r="R183" s="40"/>
-      <c r="U183" s="9" t="s">
+      <c r="U183" s="79" t="s">
         <v>1437</v>
       </c>
-      <c r="V183" s="9" t="s">
+      <c r="V183" s="79" t="s">
         <v>1436</v>
       </c>
     </row>
@@ -15121,10 +15366,10 @@
       <c r="P184" s="40"/>
       <c r="Q184" s="40"/>
       <c r="R184" s="40"/>
-      <c r="U184" s="9" t="s">
+      <c r="U184" s="79" t="s">
         <v>1438</v>
       </c>
-      <c r="V184" s="9" t="s">
+      <c r="V184" s="79" t="s">
         <v>1436</v>
       </c>
     </row>
@@ -15168,10 +15413,10 @@
       <c r="P185" s="40"/>
       <c r="Q185" s="40"/>
       <c r="R185" s="40"/>
-      <c r="U185" s="9" t="s">
+      <c r="U185" s="79" t="s">
         <v>1439</v>
       </c>
-      <c r="V185" s="9" t="s">
+      <c r="V185" s="79" t="s">
         <v>1436</v>
       </c>
     </row>
@@ -15215,10 +15460,10 @@
       <c r="P186" s="40"/>
       <c r="Q186" s="40"/>
       <c r="R186" s="40"/>
-      <c r="U186" s="9" t="s">
+      <c r="U186" s="79" t="s">
         <v>1440</v>
       </c>
-      <c r="V186" s="9" t="s">
+      <c r="V186" s="79" t="s">
         <v>1441</v>
       </c>
     </row>
@@ -15262,10 +15507,10 @@
       <c r="P187" s="40"/>
       <c r="Q187" s="40"/>
       <c r="R187" s="40"/>
-      <c r="U187" s="9" t="s">
+      <c r="U187" s="79" t="s">
         <v>1442</v>
       </c>
-      <c r="V187" s="9" t="s">
+      <c r="V187" s="79" t="s">
         <v>1441</v>
       </c>
     </row>
@@ -15309,10 +15554,10 @@
       <c r="P188" s="40"/>
       <c r="Q188" s="40"/>
       <c r="R188" s="40"/>
-      <c r="U188" s="9" t="s">
+      <c r="U188" s="79" t="s">
         <v>1443</v>
       </c>
-      <c r="V188" s="9" t="s">
+      <c r="V188" s="79" t="s">
         <v>1444</v>
       </c>
     </row>
@@ -15356,10 +15601,10 @@
       <c r="P189" s="40"/>
       <c r="Q189" s="40"/>
       <c r="R189" s="40"/>
-      <c r="U189" s="9" t="s">
+      <c r="U189" s="79" t="s">
         <v>1445</v>
       </c>
-      <c r="V189" s="9" t="s">
+      <c r="V189" s="79" t="s">
         <v>1444</v>
       </c>
     </row>
@@ -15403,10 +15648,10 @@
       <c r="P190" s="40"/>
       <c r="Q190" s="40"/>
       <c r="R190" s="40"/>
-      <c r="U190" s="9" t="s">
+      <c r="U190" s="79" t="s">
         <v>1446</v>
       </c>
-      <c r="V190" s="9" t="s">
+      <c r="V190" s="79" t="s">
         <v>1444</v>
       </c>
     </row>
@@ -15450,10 +15695,10 @@
       <c r="P191" s="40"/>
       <c r="Q191" s="40"/>
       <c r="R191" s="40"/>
-      <c r="U191" s="9" t="s">
+      <c r="U191" s="79" t="s">
         <v>1447</v>
       </c>
-      <c r="V191" s="9" t="s">
+      <c r="V191" s="79" t="s">
         <v>1448</v>
       </c>
     </row>
@@ -15497,10 +15742,10 @@
       <c r="P192" s="40"/>
       <c r="Q192" s="40"/>
       <c r="R192" s="40"/>
-      <c r="U192" s="9" t="s">
+      <c r="U192" s="79" t="s">
         <v>1449</v>
       </c>
-      <c r="V192" s="9" t="s">
+      <c r="V192" s="79" t="s">
         <v>1448</v>
       </c>
     </row>
@@ -15544,10 +15789,10 @@
       <c r="P193" s="40"/>
       <c r="Q193" s="40"/>
       <c r="R193" s="40"/>
-      <c r="U193" s="9" t="s">
+      <c r="U193" s="79" t="s">
         <v>1450</v>
       </c>
-      <c r="V193" s="9" t="s">
+      <c r="V193" s="79" t="s">
         <v>1448</v>
       </c>
     </row>
@@ -15591,10 +15836,10 @@
       <c r="P194" s="40"/>
       <c r="Q194" s="40"/>
       <c r="R194" s="40"/>
-      <c r="U194" s="9" t="s">
+      <c r="U194" s="79" t="s">
         <v>1451</v>
       </c>
-      <c r="V194" s="9" t="s">
+      <c r="V194" s="79" t="s">
         <v>1448</v>
       </c>
     </row>
@@ -15638,10 +15883,10 @@
       <c r="P195" s="40"/>
       <c r="Q195" s="40"/>
       <c r="R195" s="40"/>
-      <c r="U195" s="9" t="s">
+      <c r="U195" s="79" t="s">
         <v>1452</v>
       </c>
-      <c r="V195" s="9" t="s">
+      <c r="V195" s="79" t="s">
         <v>1453</v>
       </c>
     </row>
@@ -15685,10 +15930,10 @@
       <c r="P196" s="40"/>
       <c r="Q196" s="40"/>
       <c r="R196" s="40"/>
-      <c r="U196" s="9" t="s">
+      <c r="U196" s="79" t="s">
         <v>1454</v>
       </c>
-      <c r="V196" s="9" t="s">
+      <c r="V196" s="79" t="s">
         <v>1453</v>
       </c>
     </row>
@@ -15732,10 +15977,10 @@
       <c r="P197" s="40"/>
       <c r="Q197" s="40"/>
       <c r="R197" s="40"/>
-      <c r="U197" s="9" t="s">
+      <c r="U197" s="79" t="s">
         <v>1455</v>
       </c>
-      <c r="V197" s="9" t="s">
+      <c r="V197" s="79" t="s">
         <v>1456</v>
       </c>
     </row>
@@ -15779,10 +16024,10 @@
       <c r="P198" s="40"/>
       <c r="Q198" s="40"/>
       <c r="R198" s="40"/>
-      <c r="U198" s="9" t="s">
+      <c r="U198" s="79" t="s">
         <v>1457</v>
       </c>
-      <c r="V198" s="9" t="s">
+      <c r="V198" s="79" t="s">
         <v>1456</v>
       </c>
     </row>
@@ -15826,10 +16071,10 @@
       <c r="P199" s="40"/>
       <c r="Q199" s="40"/>
       <c r="R199" s="40"/>
-      <c r="U199" s="9" t="s">
+      <c r="U199" s="79" t="s">
         <v>1458</v>
       </c>
-      <c r="V199" s="9" t="s">
+      <c r="V199" s="79" t="s">
         <v>1456</v>
       </c>
     </row>
@@ -15873,10 +16118,10 @@
       <c r="P200" s="40"/>
       <c r="Q200" s="40"/>
       <c r="R200" s="40"/>
-      <c r="U200" s="9" t="s">
+      <c r="U200" s="79" t="s">
         <v>1459</v>
       </c>
-      <c r="V200" s="9" t="s">
+      <c r="V200" s="79" t="s">
         <v>1460</v>
       </c>
     </row>
@@ -15920,10 +16165,10 @@
       <c r="P201" s="40"/>
       <c r="Q201" s="40"/>
       <c r="R201" s="40"/>
-      <c r="U201" s="9" t="s">
+      <c r="U201" s="79" t="s">
         <v>1461</v>
       </c>
-      <c r="V201" s="9" t="s">
+      <c r="V201" s="79" t="s">
         <v>1462</v>
       </c>
     </row>
@@ -15967,10 +16212,10 @@
       <c r="P202" s="40"/>
       <c r="Q202" s="40"/>
       <c r="R202" s="40"/>
-      <c r="U202" s="9" t="s">
+      <c r="U202" s="79" t="s">
         <v>1463</v>
       </c>
-      <c r="V202" s="9" t="s">
+      <c r="V202" s="79" t="s">
         <v>1462</v>
       </c>
     </row>
@@ -16014,10 +16259,10 @@
       <c r="P203" s="40"/>
       <c r="Q203" s="40"/>
       <c r="R203" s="40"/>
-      <c r="U203" s="9" t="s">
+      <c r="U203" s="79" t="s">
         <v>1464</v>
       </c>
-      <c r="V203" s="9" t="s">
+      <c r="V203" s="79" t="s">
         <v>1462</v>
       </c>
     </row>
@@ -16061,10 +16306,10 @@
       <c r="P204" s="40"/>
       <c r="Q204" s="40"/>
       <c r="R204" s="40"/>
-      <c r="U204" s="9" t="s">
+      <c r="U204" s="79" t="s">
         <v>1465</v>
       </c>
-      <c r="V204" s="9" t="s">
+      <c r="V204" s="79" t="s">
         <v>1462</v>
       </c>
     </row>
@@ -16108,10 +16353,10 @@
       <c r="P205" s="40"/>
       <c r="Q205" s="40"/>
       <c r="R205" s="40"/>
-      <c r="U205" s="9" t="s">
+      <c r="U205" s="79" t="s">
         <v>1466</v>
       </c>
-      <c r="V205" s="9" t="s">
+      <c r="V205" s="79" t="s">
         <v>1467</v>
       </c>
     </row>
@@ -16155,10 +16400,10 @@
       <c r="P206" s="40"/>
       <c r="Q206" s="40"/>
       <c r="R206" s="40"/>
-      <c r="U206" s="9" t="s">
+      <c r="U206" s="79" t="s">
         <v>1468</v>
       </c>
-      <c r="V206" s="9" t="s">
+      <c r="V206" s="79" t="s">
         <v>1467</v>
       </c>
     </row>
@@ -16202,10 +16447,10 @@
       <c r="P207" s="40"/>
       <c r="Q207" s="40"/>
       <c r="R207" s="40"/>
-      <c r="U207" s="9" t="s">
+      <c r="U207" s="79" t="s">
         <v>1469</v>
       </c>
-      <c r="V207" s="9" t="s">
+      <c r="V207" s="79" t="s">
         <v>1467</v>
       </c>
     </row>
@@ -16249,10 +16494,10 @@
       <c r="P208" s="40"/>
       <c r="Q208" s="40"/>
       <c r="R208" s="40"/>
-      <c r="U208" s="9" t="s">
+      <c r="U208" s="79" t="s">
         <v>1470</v>
       </c>
-      <c r="V208" s="9" t="s">
+      <c r="V208" s="79" t="s">
         <v>1467</v>
       </c>
     </row>
@@ -16296,10 +16541,10 @@
       <c r="P209" s="40"/>
       <c r="Q209" s="40"/>
       <c r="R209" s="40"/>
-      <c r="U209" s="9" t="s">
+      <c r="U209" s="79" t="s">
         <v>1471</v>
       </c>
-      <c r="V209" s="9" t="s">
+      <c r="V209" s="79" t="s">
         <v>1467</v>
       </c>
     </row>
@@ -16343,10 +16588,10 @@
       <c r="P210" s="40"/>
       <c r="Q210" s="40"/>
       <c r="R210" s="40"/>
-      <c r="U210" s="9" t="s">
+      <c r="U210" s="79" t="s">
         <v>1472</v>
       </c>
-      <c r="V210" s="9" t="s">
+      <c r="V210" s="79" t="s">
         <v>1473</v>
       </c>
     </row>
@@ -16390,10 +16635,10 @@
       <c r="P211" s="40"/>
       <c r="Q211" s="40"/>
       <c r="R211" s="40"/>
-      <c r="U211" s="9" t="s">
+      <c r="U211" s="79" t="s">
         <v>1474</v>
       </c>
-      <c r="V211" s="9" t="s">
+      <c r="V211" s="79" t="s">
         <v>1473</v>
       </c>
     </row>
@@ -16437,10 +16682,10 @@
       <c r="P212" s="40"/>
       <c r="Q212" s="40"/>
       <c r="R212" s="40"/>
-      <c r="U212" s="9" t="s">
+      <c r="U212" s="79" t="s">
         <v>1475</v>
       </c>
-      <c r="V212" s="9" t="s">
+      <c r="V212" s="79" t="s">
         <v>1473</v>
       </c>
     </row>
@@ -16484,10 +16729,10 @@
       <c r="P213" s="40"/>
       <c r="Q213" s="40"/>
       <c r="R213" s="40"/>
-      <c r="U213" s="9" t="s">
+      <c r="U213" s="79" t="s">
         <v>1476</v>
       </c>
-      <c r="V213" s="9" t="s">
+      <c r="V213" s="79" t="s">
         <v>1473</v>
       </c>
     </row>
@@ -16531,10 +16776,10 @@
       <c r="P214" s="40"/>
       <c r="Q214" s="40"/>
       <c r="R214" s="40"/>
-      <c r="U214" s="9" t="s">
+      <c r="U214" s="79" t="s">
         <v>1477</v>
       </c>
-      <c r="V214" s="9" t="s">
+      <c r="V214" s="79" t="s">
         <v>1473</v>
       </c>
     </row>
@@ -16578,10 +16823,10 @@
       <c r="P215" s="40"/>
       <c r="Q215" s="40"/>
       <c r="R215" s="40"/>
-      <c r="U215" s="9" t="s">
+      <c r="U215" s="79" t="s">
         <v>1478</v>
       </c>
-      <c r="V215" s="9" t="s">
+      <c r="V215" s="79" t="s">
         <v>1479</v>
       </c>
     </row>
@@ -16625,10 +16870,10 @@
       <c r="P216" s="40"/>
       <c r="Q216" s="40"/>
       <c r="R216" s="40"/>
-      <c r="U216" s="9" t="s">
+      <c r="U216" s="79" t="s">
         <v>1480</v>
       </c>
-      <c r="V216" s="9" t="s">
+      <c r="V216" s="79" t="s">
         <v>1479</v>
       </c>
     </row>
@@ -16672,10 +16917,10 @@
       <c r="P217" s="40"/>
       <c r="Q217" s="40"/>
       <c r="R217" s="40"/>
-      <c r="U217" s="9" t="s">
+      <c r="U217" s="79" t="s">
         <v>1481</v>
       </c>
-      <c r="V217" s="9" t="s">
+      <c r="V217" s="79" t="s">
         <v>1479</v>
       </c>
     </row>
@@ -16719,10 +16964,10 @@
       <c r="P218" s="40"/>
       <c r="Q218" s="40"/>
       <c r="R218" s="40"/>
-      <c r="U218" s="9" t="s">
+      <c r="U218" s="79" t="s">
         <v>1482</v>
       </c>
-      <c r="V218" s="9" t="s">
+      <c r="V218" s="79" t="s">
         <v>1483</v>
       </c>
     </row>
@@ -16766,10 +17011,10 @@
       <c r="P219" s="40"/>
       <c r="Q219" s="40"/>
       <c r="R219" s="40"/>
-      <c r="U219" s="9" t="s">
+      <c r="U219" s="79" t="s">
         <v>1484</v>
       </c>
-      <c r="V219" s="9" t="s">
+      <c r="V219" s="79" t="s">
         <v>1483</v>
       </c>
     </row>
@@ -16813,10 +17058,10 @@
       <c r="P220" s="40"/>
       <c r="Q220" s="40"/>
       <c r="R220" s="40"/>
-      <c r="U220" s="9" t="s">
+      <c r="U220" s="79" t="s">
         <v>1485</v>
       </c>
-      <c r="V220" s="9" t="s">
+      <c r="V220" s="79" t="s">
         <v>1483</v>
       </c>
     </row>
@@ -16860,10 +17105,10 @@
       <c r="P221" s="40"/>
       <c r="Q221" s="40"/>
       <c r="R221" s="40"/>
-      <c r="U221" s="9" t="s">
+      <c r="U221" s="79" t="s">
         <v>1486</v>
       </c>
-      <c r="V221" s="9" t="s">
+      <c r="V221" s="79" t="s">
         <v>1487</v>
       </c>
     </row>
@@ -16907,10 +17152,10 @@
       <c r="P222" s="40"/>
       <c r="Q222" s="40"/>
       <c r="R222" s="40"/>
-      <c r="U222" s="9" t="s">
+      <c r="U222" s="79" t="s">
         <v>1488</v>
       </c>
-      <c r="V222" s="9" t="s">
+      <c r="V222" s="79" t="s">
         <v>1489</v>
       </c>
     </row>
@@ -16954,10 +17199,10 @@
       <c r="P223" s="40"/>
       <c r="Q223" s="40"/>
       <c r="R223" s="40"/>
-      <c r="U223" s="9" t="s">
+      <c r="U223" s="79" t="s">
         <v>1490</v>
       </c>
-      <c r="V223" s="9" t="s">
+      <c r="V223" s="79" t="s">
         <v>1489</v>
       </c>
     </row>
@@ -17001,10 +17246,10 @@
       <c r="P224" s="40"/>
       <c r="Q224" s="40"/>
       <c r="R224" s="40"/>
-      <c r="U224" s="9" t="s">
+      <c r="U224" s="79" t="s">
         <v>1491</v>
       </c>
-      <c r="V224" s="9" t="s">
+      <c r="V224" s="79" t="s">
         <v>1489</v>
       </c>
     </row>
@@ -17048,10 +17293,10 @@
       <c r="P225" s="40"/>
       <c r="Q225" s="40"/>
       <c r="R225" s="40"/>
-      <c r="U225" s="9" t="s">
+      <c r="U225" s="79" t="s">
         <v>1492</v>
       </c>
-      <c r="V225" s="9" t="s">
+      <c r="V225" s="79" t="s">
         <v>1489</v>
       </c>
     </row>
@@ -17095,10 +17340,10 @@
       <c r="P226" s="40"/>
       <c r="Q226" s="40"/>
       <c r="R226" s="40"/>
-      <c r="U226" s="9" t="s">
+      <c r="U226" s="79" t="s">
         <v>1493</v>
       </c>
-      <c r="V226" s="9" t="s">
+      <c r="V226" s="79" t="s">
         <v>1494</v>
       </c>
     </row>
@@ -17142,10 +17387,10 @@
       <c r="P227" s="40"/>
       <c r="Q227" s="40"/>
       <c r="R227" s="40"/>
-      <c r="U227" s="9" t="s">
+      <c r="U227" s="79" t="s">
         <v>1495</v>
       </c>
-      <c r="V227" s="9" t="s">
+      <c r="V227" s="79" t="s">
         <v>1494</v>
       </c>
     </row>
@@ -17189,10 +17434,10 @@
       <c r="P228" s="40"/>
       <c r="Q228" s="40"/>
       <c r="R228" s="40"/>
-      <c r="U228" s="9" t="s">
+      <c r="U228" s="79" t="s">
         <v>1496</v>
       </c>
-      <c r="V228" s="9" t="s">
+      <c r="V228" s="79" t="s">
         <v>1494</v>
       </c>
     </row>
@@ -17236,10 +17481,10 @@
       <c r="P229" s="40"/>
       <c r="Q229" s="40"/>
       <c r="R229" s="40"/>
-      <c r="U229" s="9" t="s">
+      <c r="U229" s="79" t="s">
         <v>1497</v>
       </c>
-      <c r="V229" s="9" t="s">
+      <c r="V229" s="79" t="s">
         <v>1498</v>
       </c>
     </row>
@@ -17283,10 +17528,10 @@
       <c r="P230" s="40"/>
       <c r="Q230" s="40"/>
       <c r="R230" s="40"/>
-      <c r="U230" s="9" t="s">
+      <c r="U230" s="79" t="s">
         <v>1499</v>
       </c>
-      <c r="V230" s="9" t="s">
+      <c r="V230" s="79" t="s">
         <v>1494</v>
       </c>
     </row>
@@ -17330,10 +17575,10 @@
       <c r="P231" s="40"/>
       <c r="Q231" s="40"/>
       <c r="R231" s="40"/>
-      <c r="U231" s="9" t="s">
+      <c r="U231" s="79" t="s">
         <v>1500</v>
       </c>
-      <c r="V231" s="9" t="s">
+      <c r="V231" s="79" t="s">
         <v>1501</v>
       </c>
     </row>
@@ -17377,10 +17622,10 @@
       <c r="P232" s="40"/>
       <c r="Q232" s="40"/>
       <c r="R232" s="40"/>
-      <c r="U232" s="9" t="s">
+      <c r="U232" s="79" t="s">
         <v>1502</v>
       </c>
-      <c r="V232" s="9" t="s">
+      <c r="V232" s="79" t="s">
         <v>1503</v>
       </c>
     </row>
@@ -17424,10 +17669,10 @@
       <c r="P233" s="40"/>
       <c r="Q233" s="40"/>
       <c r="R233" s="40"/>
-      <c r="U233" s="9" t="s">
+      <c r="U233" s="79" t="s">
         <v>1504</v>
       </c>
-      <c r="V233" s="9" t="s">
+      <c r="V233" s="79" t="s">
         <v>1503</v>
       </c>
     </row>
@@ -17471,10 +17716,10 @@
       <c r="P234" s="40"/>
       <c r="Q234" s="40"/>
       <c r="R234" s="40"/>
-      <c r="U234" s="9" t="s">
+      <c r="U234" s="79" t="s">
         <v>1505</v>
       </c>
-      <c r="V234" s="9" t="s">
+      <c r="V234" s="79" t="s">
         <v>1503</v>
       </c>
     </row>
@@ -17518,10 +17763,10 @@
       <c r="P235" s="40"/>
       <c r="Q235" s="40"/>
       <c r="R235" s="40"/>
-      <c r="U235" s="9" t="s">
+      <c r="U235" s="79" t="s">
         <v>1506</v>
       </c>
-      <c r="V235" s="9" t="s">
+      <c r="V235" s="79" t="s">
         <v>1507</v>
       </c>
     </row>
@@ -17565,10 +17810,10 @@
       <c r="P236" s="40"/>
       <c r="Q236" s="40"/>
       <c r="R236" s="40"/>
-      <c r="U236" s="9" t="s">
+      <c r="U236" s="79" t="s">
         <v>1508</v>
       </c>
-      <c r="V236" s="9" t="s">
+      <c r="V236" s="79" t="s">
         <v>1507</v>
       </c>
     </row>
@@ -17612,10 +17857,10 @@
       <c r="P237" s="40"/>
       <c r="Q237" s="40"/>
       <c r="R237" s="40"/>
-      <c r="U237" s="9" t="s">
+      <c r="U237" s="79" t="s">
         <v>1509</v>
       </c>
-      <c r="V237" s="9" t="s">
+      <c r="V237" s="79" t="s">
         <v>1510</v>
       </c>
     </row>
@@ -17659,10 +17904,10 @@
       <c r="P238" s="40"/>
       <c r="Q238" s="40"/>
       <c r="R238" s="40"/>
-      <c r="U238" s="9" t="s">
+      <c r="U238" s="79" t="s">
         <v>1511</v>
       </c>
-      <c r="V238" s="9" t="s">
+      <c r="V238" s="79" t="s">
         <v>1510</v>
       </c>
     </row>
@@ -17706,10 +17951,10 @@
       <c r="P239" s="40"/>
       <c r="Q239" s="40"/>
       <c r="R239" s="40"/>
-      <c r="U239" s="9" t="s">
+      <c r="U239" s="79" t="s">
         <v>1512</v>
       </c>
-      <c r="V239" s="9" t="s">
+      <c r="V239" s="79" t="s">
         <v>1510</v>
       </c>
     </row>
@@ -17753,10 +17998,10 @@
       <c r="P240" s="40"/>
       <c r="Q240" s="40"/>
       <c r="R240" s="40"/>
-      <c r="U240" s="9" t="s">
+      <c r="U240" s="79" t="s">
         <v>1513</v>
       </c>
-      <c r="V240" s="9" t="s">
+      <c r="V240" s="79" t="s">
         <v>1514</v>
       </c>
     </row>
@@ -17800,10 +18045,10 @@
       <c r="P241" s="40"/>
       <c r="Q241" s="40"/>
       <c r="R241" s="40"/>
-      <c r="U241" s="9" t="s">
+      <c r="U241" s="79" t="s">
         <v>1515</v>
       </c>
-      <c r="V241" s="9" t="s">
+      <c r="V241" s="79" t="s">
         <v>1514</v>
       </c>
     </row>
@@ -17847,10 +18092,10 @@
       <c r="P242" s="40"/>
       <c r="Q242" s="40"/>
       <c r="R242" s="40"/>
-      <c r="U242" s="9" t="s">
+      <c r="U242" s="79" t="s">
         <v>1516</v>
       </c>
-      <c r="V242" s="9" t="s">
+      <c r="V242" s="79" t="s">
         <v>1514</v>
       </c>
     </row>
@@ -17894,10 +18139,10 @@
       <c r="P243" s="40"/>
       <c r="Q243" s="40"/>
       <c r="R243" s="40"/>
-      <c r="U243" s="9" t="s">
+      <c r="U243" s="79" t="s">
         <v>1517</v>
       </c>
-      <c r="V243" s="9" t="s">
+      <c r="V243" s="79" t="s">
         <v>1518</v>
       </c>
     </row>
@@ -17941,10 +18186,10 @@
       <c r="P244" s="40"/>
       <c r="Q244" s="40"/>
       <c r="R244" s="40"/>
-      <c r="U244" s="9" t="s">
+      <c r="U244" s="79" t="s">
         <v>1519</v>
       </c>
-      <c r="V244" s="9" t="s">
+      <c r="V244" s="79" t="s">
         <v>1518</v>
       </c>
     </row>
@@ -17988,10 +18233,10 @@
       <c r="P245" s="40"/>
       <c r="Q245" s="40"/>
       <c r="R245" s="40"/>
-      <c r="U245" s="9" t="s">
+      <c r="U245" s="79" t="s">
         <v>1520</v>
       </c>
-      <c r="V245" s="9" t="s">
+      <c r="V245" s="79" t="s">
         <v>1521</v>
       </c>
     </row>
@@ -18035,10 +18280,10 @@
       <c r="P246" s="40"/>
       <c r="Q246" s="40"/>
       <c r="R246" s="40"/>
-      <c r="U246" s="9" t="s">
+      <c r="U246" s="79" t="s">
         <v>1522</v>
       </c>
-      <c r="V246" s="9" t="s">
+      <c r="V246" s="79" t="s">
         <v>1521</v>
       </c>
     </row>
@@ -18082,10 +18327,10 @@
       <c r="P247" s="40"/>
       <c r="Q247" s="40"/>
       <c r="R247" s="40"/>
-      <c r="U247" s="9" t="s">
+      <c r="U247" s="79" t="s">
         <v>1523</v>
       </c>
-      <c r="V247" s="9" t="s">
+      <c r="V247" s="79" t="s">
         <v>1524</v>
       </c>
     </row>
@@ -18129,10 +18374,10 @@
       <c r="P248" s="40"/>
       <c r="Q248" s="40"/>
       <c r="R248" s="40"/>
-      <c r="U248" s="9" t="s">
+      <c r="U248" s="79" t="s">
         <v>1525</v>
       </c>
-      <c r="V248" s="9" t="s">
+      <c r="V248" s="79" t="s">
         <v>1524</v>
       </c>
     </row>
@@ -18176,10 +18421,10 @@
       <c r="P249" s="40"/>
       <c r="Q249" s="40"/>
       <c r="R249" s="40"/>
-      <c r="U249" s="9" t="s">
+      <c r="U249" s="79" t="s">
         <v>1526</v>
       </c>
-      <c r="V249" s="9" t="s">
+      <c r="V249" s="79" t="s">
         <v>1527</v>
       </c>
     </row>
@@ -18223,10 +18468,10 @@
       <c r="P250" s="40"/>
       <c r="Q250" s="40"/>
       <c r="R250" s="40"/>
-      <c r="U250" s="9" t="s">
+      <c r="U250" s="79" t="s">
         <v>1528</v>
       </c>
-      <c r="V250" s="9" t="s">
+      <c r="V250" s="79" t="s">
         <v>1527</v>
       </c>
     </row>
@@ -18270,10 +18515,10 @@
       <c r="P251" s="40"/>
       <c r="Q251" s="40"/>
       <c r="R251" s="40"/>
-      <c r="U251" s="9" t="s">
+      <c r="U251" s="79" t="s">
         <v>1529</v>
       </c>
-      <c r="V251" s="9" t="s">
+      <c r="V251" s="79" t="s">
         <v>1527</v>
       </c>
     </row>
@@ -18317,10 +18562,10 @@
       <c r="P252" s="40"/>
       <c r="Q252" s="40"/>
       <c r="R252" s="40"/>
-      <c r="U252" s="9" t="s">
+      <c r="U252" s="79" t="s">
         <v>1530</v>
       </c>
-      <c r="V252" s="9" t="s">
+      <c r="V252" s="79" t="s">
         <v>1527</v>
       </c>
     </row>
@@ -18364,10 +18609,10 @@
       <c r="P253" s="40"/>
       <c r="Q253" s="40"/>
       <c r="R253" s="40"/>
-      <c r="U253" s="9" t="s">
+      <c r="U253" s="79" t="s">
         <v>1531</v>
       </c>
-      <c r="V253" s="9" t="s">
+      <c r="V253" s="79" t="s">
         <v>1532</v>
       </c>
     </row>
@@ -18411,10 +18656,10 @@
       <c r="P254" s="40"/>
       <c r="Q254" s="40"/>
       <c r="R254" s="40"/>
-      <c r="U254" s="9" t="s">
+      <c r="U254" s="79" t="s">
         <v>1533</v>
       </c>
-      <c r="V254" s="9" t="s">
+      <c r="V254" s="79" t="s">
         <v>1534</v>
       </c>
     </row>
@@ -18458,10 +18703,10 @@
       <c r="P255" s="40"/>
       <c r="Q255" s="40"/>
       <c r="R255" s="40"/>
-      <c r="U255" s="9" t="s">
+      <c r="U255" s="79" t="s">
         <v>1535</v>
       </c>
-      <c r="V255" s="9" t="s">
+      <c r="V255" s="79" t="s">
         <v>1534</v>
       </c>
     </row>
@@ -18505,10 +18750,10 @@
       <c r="P256" s="40"/>
       <c r="Q256" s="40"/>
       <c r="R256" s="40"/>
-      <c r="U256" s="9" t="s">
+      <c r="U256" s="79" t="s">
         <v>1536</v>
       </c>
-      <c r="V256" s="9" t="s">
+      <c r="V256" s="79" t="s">
         <v>1537</v>
       </c>
     </row>
@@ -18552,10 +18797,10 @@
       <c r="P257" s="40"/>
       <c r="Q257" s="40"/>
       <c r="R257" s="40"/>
-      <c r="U257" s="9" t="s">
+      <c r="U257" s="79" t="s">
         <v>1538</v>
       </c>
-      <c r="V257" s="9" t="s">
+      <c r="V257" s="79" t="s">
         <v>1537</v>
       </c>
     </row>
@@ -18599,10 +18844,10 @@
       <c r="P258" s="40"/>
       <c r="Q258" s="40"/>
       <c r="R258" s="40"/>
-      <c r="U258" s="9" t="s">
+      <c r="U258" s="79" t="s">
         <v>1539</v>
       </c>
-      <c r="V258" s="9" t="s">
+      <c r="V258" s="79" t="s">
         <v>1540</v>
       </c>
     </row>
@@ -18646,10 +18891,10 @@
       <c r="P259" s="40"/>
       <c r="Q259" s="40"/>
       <c r="R259" s="40"/>
-      <c r="U259" s="9" t="s">
+      <c r="U259" s="79" t="s">
         <v>1541</v>
       </c>
-      <c r="V259" s="9" t="s">
+      <c r="V259" s="79" t="s">
         <v>1540</v>
       </c>
     </row>
@@ -18693,10 +18938,10 @@
       <c r="P260" s="40"/>
       <c r="Q260" s="40"/>
       <c r="R260" s="40"/>
-      <c r="U260" s="9" t="s">
+      <c r="U260" s="79" t="s">
         <v>1542</v>
       </c>
-      <c r="V260" s="9" t="s">
+      <c r="V260" s="79" t="s">
         <v>1543</v>
       </c>
     </row>
@@ -18740,10 +18985,10 @@
       <c r="P261" s="40"/>
       <c r="Q261" s="40"/>
       <c r="R261" s="40"/>
-      <c r="U261" s="9" t="s">
+      <c r="U261" s="79" t="s">
         <v>1544</v>
       </c>
-      <c r="V261" s="9" t="s">
+      <c r="V261" s="79" t="s">
         <v>1545</v>
       </c>
     </row>
@@ -18787,10 +19032,10 @@
       <c r="P262" s="40"/>
       <c r="Q262" s="40"/>
       <c r="R262" s="40"/>
-      <c r="U262" s="9" t="s">
+      <c r="U262" s="79" t="s">
         <v>1546</v>
       </c>
-      <c r="V262" s="9" t="s">
+      <c r="V262" s="79" t="s">
         <v>1545</v>
       </c>
     </row>
@@ -18834,10 +19079,10 @@
       <c r="P263" s="40"/>
       <c r="Q263" s="40"/>
       <c r="R263" s="40"/>
-      <c r="U263" s="9" t="s">
+      <c r="U263" s="79" t="s">
         <v>1547</v>
       </c>
-      <c r="V263" s="9" t="s">
+      <c r="V263" s="79" t="s">
         <v>1545</v>
       </c>
     </row>
@@ -18881,10 +19126,10 @@
       <c r="P264" s="40"/>
       <c r="Q264" s="40"/>
       <c r="R264" s="40"/>
-      <c r="U264" s="9" t="s">
+      <c r="U264" s="79" t="s">
         <v>1548</v>
       </c>
-      <c r="V264" s="9" t="s">
+      <c r="V264" s="79" t="s">
         <v>1549</v>
       </c>
     </row>
@@ -18928,10 +19173,10 @@
       <c r="P265" s="40"/>
       <c r="Q265" s="40"/>
       <c r="R265" s="40"/>
-      <c r="U265" s="9" t="s">
+      <c r="U265" s="79" t="s">
         <v>1550</v>
       </c>
-      <c r="V265" s="9" t="s">
+      <c r="V265" s="79" t="s">
         <v>1549</v>
       </c>
     </row>
@@ -18975,10 +19220,10 @@
       <c r="P266" s="40"/>
       <c r="Q266" s="40"/>
       <c r="R266" s="40"/>
-      <c r="U266" s="9" t="s">
+      <c r="U266" s="79" t="s">
         <v>1551</v>
       </c>
-      <c r="V266" s="9" t="s">
+      <c r="V266" s="79" t="s">
         <v>1552</v>
       </c>
     </row>
@@ -19022,10 +19267,10 @@
       <c r="P267" s="40"/>
       <c r="Q267" s="40"/>
       <c r="R267" s="40"/>
-      <c r="U267" s="9" t="s">
+      <c r="U267" s="79" t="s">
         <v>1553</v>
       </c>
-      <c r="V267" s="9" t="s">
+      <c r="V267" s="79" t="s">
         <v>1552</v>
       </c>
     </row>
@@ -19069,10 +19314,10 @@
       <c r="P268" s="40"/>
       <c r="Q268" s="40"/>
       <c r="R268" s="40"/>
-      <c r="U268" s="9" t="s">
+      <c r="U268" s="79" t="s">
         <v>1554</v>
       </c>
-      <c r="V268" s="9" t="s">
+      <c r="V268" s="79" t="s">
         <v>1552</v>
       </c>
     </row>
@@ -19116,10 +19361,10 @@
       <c r="P269" s="40"/>
       <c r="Q269" s="40"/>
       <c r="R269" s="40"/>
-      <c r="U269" s="9" t="s">
+      <c r="U269" s="79" t="s">
         <v>1555</v>
       </c>
-      <c r="V269" s="9" t="s">
+      <c r="V269" s="79" t="s">
         <v>1556</v>
       </c>
     </row>
@@ -19163,10 +19408,10 @@
       <c r="P270" s="40"/>
       <c r="Q270" s="40"/>
       <c r="R270" s="40"/>
-      <c r="U270" s="9" t="s">
+      <c r="U270" s="79" t="s">
         <v>1557</v>
       </c>
-      <c r="V270" s="9" t="s">
+      <c r="V270" s="79" t="s">
         <v>1556</v>
       </c>
     </row>
@@ -19210,10 +19455,10 @@
       <c r="P271" s="40"/>
       <c r="Q271" s="40"/>
       <c r="R271" s="40"/>
-      <c r="U271" s="9" t="s">
+      <c r="U271" s="79" t="s">
         <v>1558</v>
       </c>
-      <c r="V271" s="9" t="s">
+      <c r="V271" s="79" t="s">
         <v>1559</v>
       </c>
     </row>
@@ -19260,8 +19505,12 @@
       <c r="S272" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U272" s="10"/>
-      <c r="V272" s="10"/>
+      <c r="U272" s="80" t="s">
+        <v>1922</v>
+      </c>
+      <c r="V272" s="80" t="s">
+        <v>1409</v>
+      </c>
     </row>
     <row r="273" spans="1:22" ht="30" customHeight="1">
       <c r="A273" s="43" t="s">
@@ -19306,8 +19555,12 @@
       <c r="S273" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U273" s="10"/>
-      <c r="V273" s="10"/>
+      <c r="U273" s="80" t="s">
+        <v>1923</v>
+      </c>
+      <c r="V273" s="80" t="s">
+        <v>1924</v>
+      </c>
     </row>
     <row r="274" spans="1:22" ht="30" customHeight="1">
       <c r="A274" s="43" t="s">
@@ -19352,8 +19605,12 @@
       <c r="S274" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U274" s="10"/>
-      <c r="V274" s="10"/>
+      <c r="U274" s="83" t="s">
+        <v>1900</v>
+      </c>
+      <c r="V274" s="83" t="s">
+        <v>1433</v>
+      </c>
     </row>
     <row r="275" spans="1:22" ht="30" customHeight="1">
       <c r="A275" s="43" t="s">
@@ -19398,8 +19655,12 @@
       <c r="S275" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U275" s="10"/>
-      <c r="V275" s="10"/>
+      <c r="U275" s="83" t="s">
+        <v>1901</v>
+      </c>
+      <c r="V275" s="83" t="s">
+        <v>1433</v>
+      </c>
     </row>
     <row r="276" spans="1:22" ht="30" customHeight="1">
       <c r="A276" s="43" t="s">
@@ -19444,8 +19705,12 @@
       <c r="S276" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U276" s="10"/>
-      <c r="V276" s="10"/>
+      <c r="U276" s="83" t="s">
+        <v>1902</v>
+      </c>
+      <c r="V276" s="83" t="s">
+        <v>1433</v>
+      </c>
     </row>
     <row r="277" spans="1:22" ht="30" customHeight="1">
       <c r="A277" s="43" t="s">
@@ -19490,8 +19755,12 @@
       <c r="S277" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U277" s="10"/>
-      <c r="V277" s="10"/>
+      <c r="U277" s="83" t="s">
+        <v>1903</v>
+      </c>
+      <c r="V277" s="83" t="s">
+        <v>1489</v>
+      </c>
     </row>
     <row r="278" spans="1:22" ht="30" customHeight="1">
       <c r="A278" s="43" t="s">
@@ -19536,8 +19805,12 @@
       <c r="S278" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U278" s="10"/>
-      <c r="V278" s="10"/>
+      <c r="U278" s="80" t="s">
+        <v>1933</v>
+      </c>
+      <c r="V278" s="80" t="s">
+        <v>1501</v>
+      </c>
     </row>
     <row r="279" spans="1:22" ht="30" customHeight="1">
       <c r="A279" s="43" t="s">
@@ -19582,8 +19855,12 @@
       <c r="S279" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U279" s="10"/>
-      <c r="V279" s="10"/>
+      <c r="U279" s="83" t="s">
+        <v>1904</v>
+      </c>
+      <c r="V279" s="83" t="s">
+        <v>1545</v>
+      </c>
     </row>
     <row r="280" spans="1:22" ht="30" customHeight="1">
       <c r="A280" s="43" t="s">
@@ -19628,8 +19905,12 @@
       <c r="S280" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U280" s="10"/>
-      <c r="V280" s="10"/>
+      <c r="U280" s="80" t="s">
+        <v>1925</v>
+      </c>
+      <c r="V280" s="80" t="s">
+        <v>1926</v>
+      </c>
     </row>
     <row r="281" spans="1:22" ht="15" customHeight="1">
       <c r="A281" s="43"/>
@@ -19651,8 +19932,8 @@
       <c r="Q281" s="40"/>
       <c r="R281" s="40"/>
       <c r="S281" s="39"/>
-      <c r="U281" s="10"/>
-      <c r="V281" s="10"/>
+      <c r="U281" s="81"/>
+      <c r="V281" s="81"/>
     </row>
     <row r="282" spans="1:22" ht="30" customHeight="1">
       <c r="A282" s="43" t="s">
@@ -19693,10 +19974,10 @@
       <c r="P282" s="40"/>
       <c r="Q282" s="40"/>
       <c r="R282" s="40"/>
-      <c r="U282" s="9" t="s">
+      <c r="U282" s="79" t="s">
         <v>1560</v>
       </c>
-      <c r="V282" s="9" t="s">
+      <c r="V282" s="79" t="s">
         <v>1561</v>
       </c>
     </row>
@@ -19740,10 +20021,10 @@
       <c r="P283" s="40"/>
       <c r="Q283" s="40"/>
       <c r="R283" s="40"/>
-      <c r="U283" s="9" t="s">
+      <c r="U283" s="79" t="s">
         <v>1562</v>
       </c>
-      <c r="V283" s="9" t="s">
+      <c r="V283" s="79" t="s">
         <v>1561</v>
       </c>
     </row>
@@ -19787,10 +20068,10 @@
       <c r="P284" s="40"/>
       <c r="Q284" s="40"/>
       <c r="R284" s="40"/>
-      <c r="U284" s="9" t="s">
+      <c r="U284" s="79" t="s">
         <v>1563</v>
       </c>
-      <c r="V284" s="9" t="s">
+      <c r="V284" s="79" t="s">
         <v>1561</v>
       </c>
     </row>
@@ -19834,10 +20115,10 @@
       <c r="P285" s="40"/>
       <c r="Q285" s="40"/>
       <c r="R285" s="40"/>
-      <c r="U285" s="9" t="s">
+      <c r="U285" s="79" t="s">
         <v>1564</v>
       </c>
-      <c r="V285" s="9" t="s">
+      <c r="V285" s="79" t="s">
         <v>1561</v>
       </c>
     </row>
@@ -19881,10 +20162,10 @@
       <c r="P286" s="40"/>
       <c r="Q286" s="40"/>
       <c r="R286" s="40"/>
-      <c r="U286" s="9" t="s">
+      <c r="U286" s="79" t="s">
         <v>1565</v>
       </c>
-      <c r="V286" s="9" t="s">
+      <c r="V286" s="79" t="s">
         <v>1566</v>
       </c>
     </row>
@@ -19928,10 +20209,10 @@
       <c r="P287" s="40"/>
       <c r="Q287" s="40"/>
       <c r="R287" s="40"/>
-      <c r="U287" s="9" t="s">
+      <c r="U287" s="79" t="s">
         <v>1567</v>
       </c>
-      <c r="V287" s="9" t="s">
+      <c r="V287" s="79" t="s">
         <v>1566</v>
       </c>
     </row>
@@ -19975,10 +20256,10 @@
       <c r="P288" s="40"/>
       <c r="Q288" s="40"/>
       <c r="R288" s="40"/>
-      <c r="U288" s="9" t="s">
+      <c r="U288" s="79" t="s">
         <v>1568</v>
       </c>
-      <c r="V288" s="9" t="s">
+      <c r="V288" s="79" t="s">
         <v>1566</v>
       </c>
     </row>
@@ -20022,10 +20303,10 @@
       <c r="P289" s="40"/>
       <c r="Q289" s="40"/>
       <c r="R289" s="40"/>
-      <c r="U289" s="9" t="s">
+      <c r="U289" s="79" t="s">
         <v>1569</v>
       </c>
-      <c r="V289" s="9" t="s">
+      <c r="V289" s="79" t="s">
         <v>1570</v>
       </c>
     </row>
@@ -20069,10 +20350,10 @@
       <c r="P290" s="40"/>
       <c r="Q290" s="40"/>
       <c r="R290" s="40"/>
-      <c r="U290" s="9" t="s">
+      <c r="U290" s="79" t="s">
         <v>1571</v>
       </c>
-      <c r="V290" s="9" t="s">
+      <c r="V290" s="79" t="s">
         <v>1570</v>
       </c>
     </row>
@@ -20116,10 +20397,10 @@
       <c r="P291" s="40"/>
       <c r="Q291" s="40"/>
       <c r="R291" s="40"/>
-      <c r="U291" s="9" t="s">
+      <c r="U291" s="79" t="s">
         <v>1572</v>
       </c>
-      <c r="V291" s="9" t="s">
+      <c r="V291" s="79" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -20163,10 +20444,10 @@
       <c r="P292" s="40"/>
       <c r="Q292" s="40"/>
       <c r="R292" s="40"/>
-      <c r="U292" s="9" t="s">
+      <c r="U292" s="79" t="s">
         <v>1574</v>
       </c>
-      <c r="V292" s="9" t="s">
+      <c r="V292" s="79" t="s">
         <v>1573</v>
       </c>
     </row>
@@ -20210,10 +20491,10 @@
       <c r="P293" s="40"/>
       <c r="Q293" s="40"/>
       <c r="R293" s="40"/>
-      <c r="U293" s="9" t="s">
+      <c r="U293" s="79" t="s">
         <v>1575</v>
       </c>
-      <c r="V293" s="9" t="s">
+      <c r="V293" s="79" t="s">
         <v>1576</v>
       </c>
     </row>
@@ -20257,10 +20538,10 @@
       <c r="P294" s="40"/>
       <c r="Q294" s="40"/>
       <c r="R294" s="40"/>
-      <c r="U294" s="9" t="s">
+      <c r="U294" s="79" t="s">
         <v>1577</v>
       </c>
-      <c r="V294" s="9" t="s">
+      <c r="V294" s="79" t="s">
         <v>1576</v>
       </c>
     </row>
@@ -20304,10 +20585,10 @@
       <c r="P295" s="40"/>
       <c r="Q295" s="40"/>
       <c r="R295" s="40"/>
-      <c r="U295" s="9" t="s">
+      <c r="U295" s="79" t="s">
         <v>1578</v>
       </c>
-      <c r="V295" s="9" t="s">
+      <c r="V295" s="79" t="s">
         <v>1579</v>
       </c>
     </row>
@@ -20351,10 +20632,10 @@
       <c r="P296" s="40"/>
       <c r="Q296" s="40"/>
       <c r="R296" s="40"/>
-      <c r="U296" s="9" t="s">
+      <c r="U296" s="79" t="s">
         <v>1580</v>
       </c>
-      <c r="V296" s="9" t="s">
+      <c r="V296" s="79" t="s">
         <v>1581</v>
       </c>
     </row>
@@ -20398,10 +20679,10 @@
       <c r="P297" s="40"/>
       <c r="Q297" s="40"/>
       <c r="R297" s="40"/>
-      <c r="U297" s="9" t="s">
+      <c r="U297" s="79" t="s">
         <v>1582</v>
       </c>
-      <c r="V297" s="9" t="s">
+      <c r="V297" s="79" t="s">
         <v>1581</v>
       </c>
     </row>
@@ -20445,10 +20726,10 @@
       <c r="P298" s="40"/>
       <c r="Q298" s="40"/>
       <c r="R298" s="40"/>
-      <c r="U298" s="9" t="s">
+      <c r="U298" s="79" t="s">
         <v>1583</v>
       </c>
-      <c r="V298" s="9" t="s">
+      <c r="V298" s="79" t="s">
         <v>1581</v>
       </c>
     </row>
@@ -20492,10 +20773,10 @@
       <c r="P299" s="40"/>
       <c r="Q299" s="40"/>
       <c r="R299" s="40"/>
-      <c r="U299" s="9" t="s">
+      <c r="U299" s="79" t="s">
         <v>1584</v>
       </c>
-      <c r="V299" s="9" t="s">
+      <c r="V299" s="79" t="s">
         <v>1581</v>
       </c>
     </row>
@@ -20539,10 +20820,10 @@
       <c r="P300" s="40"/>
       <c r="Q300" s="40"/>
       <c r="R300" s="40"/>
-      <c r="U300" s="9" t="s">
+      <c r="U300" s="79" t="s">
         <v>1585</v>
       </c>
-      <c r="V300" s="9" t="s">
+      <c r="V300" s="79" t="s">
         <v>1586</v>
       </c>
     </row>
@@ -20586,10 +20867,10 @@
       <c r="P301" s="40"/>
       <c r="Q301" s="40"/>
       <c r="R301" s="40"/>
-      <c r="U301" s="9" t="s">
+      <c r="U301" s="79" t="s">
         <v>1587</v>
       </c>
-      <c r="V301" s="9" t="s">
+      <c r="V301" s="79" t="s">
         <v>1586</v>
       </c>
     </row>
@@ -20633,10 +20914,10 @@
       <c r="P302" s="40"/>
       <c r="Q302" s="40"/>
       <c r="R302" s="40"/>
-      <c r="U302" s="9" t="s">
+      <c r="U302" s="79" t="s">
         <v>1588</v>
       </c>
-      <c r="V302" s="9" t="s">
+      <c r="V302" s="79" t="s">
         <v>1589</v>
       </c>
     </row>
@@ -20680,10 +20961,10 @@
       <c r="P303" s="40"/>
       <c r="Q303" s="40"/>
       <c r="R303" s="40"/>
-      <c r="U303" s="9" t="s">
+      <c r="U303" s="79" t="s">
         <v>1590</v>
       </c>
-      <c r="V303" s="9" t="s">
+      <c r="V303" s="79" t="s">
         <v>1589</v>
       </c>
     </row>
@@ -20727,10 +21008,10 @@
       <c r="P304" s="40"/>
       <c r="Q304" s="40"/>
       <c r="R304" s="40"/>
-      <c r="U304" s="9" t="s">
+      <c r="U304" s="79" t="s">
         <v>1591</v>
       </c>
-      <c r="V304" s="9" t="s">
+      <c r="V304" s="79" t="s">
         <v>1592</v>
       </c>
     </row>
@@ -20774,10 +21055,10 @@
       <c r="P305" s="40"/>
       <c r="Q305" s="40"/>
       <c r="R305" s="40"/>
-      <c r="U305" s="9" t="s">
+      <c r="U305" s="79" t="s">
         <v>1593</v>
       </c>
-      <c r="V305" s="9" t="s">
+      <c r="V305" s="79" t="s">
         <v>1594</v>
       </c>
     </row>
@@ -20821,10 +21102,10 @@
       <c r="P306" s="40"/>
       <c r="Q306" s="40"/>
       <c r="R306" s="40"/>
-      <c r="U306" s="9" t="s">
+      <c r="U306" s="79" t="s">
         <v>1595</v>
       </c>
-      <c r="V306" s="9" t="s">
+      <c r="V306" s="79" t="s">
         <v>1596</v>
       </c>
     </row>
@@ -20868,10 +21149,10 @@
       <c r="P307" s="40"/>
       <c r="Q307" s="40"/>
       <c r="R307" s="40"/>
-      <c r="U307" s="9" t="s">
+      <c r="U307" s="79" t="s">
         <v>1597</v>
       </c>
-      <c r="V307" s="9" t="s">
+      <c r="V307" s="79" t="s">
         <v>1596</v>
       </c>
     </row>
@@ -20915,10 +21196,10 @@
       <c r="P308" s="40"/>
       <c r="Q308" s="40"/>
       <c r="R308" s="40"/>
-      <c r="U308" s="9" t="s">
+      <c r="U308" s="79" t="s">
         <v>1598</v>
       </c>
-      <c r="V308" s="9" t="s">
+      <c r="V308" s="79" t="s">
         <v>1596</v>
       </c>
     </row>
@@ -20962,10 +21243,10 @@
       <c r="P309" s="40"/>
       <c r="Q309" s="40"/>
       <c r="R309" s="40"/>
-      <c r="U309" s="9" t="s">
+      <c r="U309" s="79" t="s">
         <v>1599</v>
       </c>
-      <c r="V309" s="9" t="s">
+      <c r="V309" s="79" t="s">
         <v>1596</v>
       </c>
     </row>
@@ -21009,10 +21290,10 @@
       <c r="P310" s="40"/>
       <c r="Q310" s="40"/>
       <c r="R310" s="40"/>
-      <c r="U310" s="9" t="s">
+      <c r="U310" s="79" t="s">
         <v>1600</v>
       </c>
-      <c r="V310" s="9" t="s">
+      <c r="V310" s="79" t="s">
         <v>1601</v>
       </c>
     </row>
@@ -21056,10 +21337,10 @@
       <c r="P311" s="40"/>
       <c r="Q311" s="40"/>
       <c r="R311" s="40"/>
-      <c r="U311" s="9" t="s">
+      <c r="U311" s="79" t="s">
         <v>1602</v>
       </c>
-      <c r="V311" s="9" t="s">
+      <c r="V311" s="79" t="s">
         <v>1601</v>
       </c>
     </row>
@@ -21103,10 +21384,10 @@
       <c r="P312" s="40"/>
       <c r="Q312" s="40"/>
       <c r="R312" s="40"/>
-      <c r="U312" s="9" t="s">
+      <c r="U312" s="79" t="s">
         <v>1603</v>
       </c>
-      <c r="V312" s="9" t="s">
+      <c r="V312" s="79" t="s">
         <v>1601</v>
       </c>
     </row>
@@ -21150,10 +21431,10 @@
       <c r="P313" s="40"/>
       <c r="Q313" s="40"/>
       <c r="R313" s="40"/>
-      <c r="U313" s="9" t="s">
+      <c r="U313" s="79" t="s">
         <v>1604</v>
       </c>
-      <c r="V313" s="9" t="s">
+      <c r="V313" s="79" t="s">
         <v>1601</v>
       </c>
     </row>
@@ -21197,10 +21478,10 @@
       <c r="P314" s="40"/>
       <c r="Q314" s="40"/>
       <c r="R314" s="40"/>
-      <c r="U314" s="9" t="s">
+      <c r="U314" s="79" t="s">
         <v>1605</v>
       </c>
-      <c r="V314" s="9" t="s">
+      <c r="V314" s="79" t="s">
         <v>1606</v>
       </c>
     </row>
@@ -21244,10 +21525,10 @@
       <c r="P315" s="40"/>
       <c r="Q315" s="40"/>
       <c r="R315" s="40"/>
-      <c r="U315" s="9" t="s">
+      <c r="U315" s="79" t="s">
         <v>1607</v>
       </c>
-      <c r="V315" s="9" t="s">
+      <c r="V315" s="79" t="s">
         <v>1606</v>
       </c>
     </row>
@@ -21291,10 +21572,10 @@
       <c r="P316" s="40"/>
       <c r="Q316" s="40"/>
       <c r="R316" s="40"/>
-      <c r="U316" s="9" t="s">
+      <c r="U316" s="79" t="s">
         <v>1608</v>
       </c>
-      <c r="V316" s="9" t="s">
+      <c r="V316" s="79" t="s">
         <v>1609</v>
       </c>
     </row>
@@ -21338,10 +21619,10 @@
       <c r="P317" s="40"/>
       <c r="Q317" s="40"/>
       <c r="R317" s="40"/>
-      <c r="U317" s="9" t="s">
+      <c r="U317" s="79" t="s">
         <v>1610</v>
       </c>
-      <c r="V317" s="9" t="s">
+      <c r="V317" s="79" t="s">
         <v>1609</v>
       </c>
     </row>
@@ -21385,10 +21666,10 @@
       <c r="P318" s="40"/>
       <c r="Q318" s="40"/>
       <c r="R318" s="40"/>
-      <c r="U318" s="9" t="s">
+      <c r="U318" s="79" t="s">
         <v>1611</v>
       </c>
-      <c r="V318" s="9" t="s">
+      <c r="V318" s="79" t="s">
         <v>1609</v>
       </c>
     </row>
@@ -21432,10 +21713,10 @@
       <c r="P319" s="40"/>
       <c r="Q319" s="40"/>
       <c r="R319" s="40"/>
-      <c r="U319" s="9" t="s">
+      <c r="U319" s="79" t="s">
         <v>1612</v>
       </c>
-      <c r="V319" s="9" t="s">
+      <c r="V319" s="79" t="s">
         <v>1609</v>
       </c>
     </row>
@@ -21479,10 +21760,10 @@
       <c r="P320" s="40"/>
       <c r="Q320" s="40"/>
       <c r="R320" s="40"/>
-      <c r="U320" s="9" t="s">
+      <c r="U320" s="79" t="s">
         <v>1613</v>
       </c>
-      <c r="V320" s="9" t="s">
+      <c r="V320" s="79" t="s">
         <v>1614</v>
       </c>
     </row>
@@ -21526,10 +21807,10 @@
       <c r="P321" s="40"/>
       <c r="Q321" s="40"/>
       <c r="R321" s="40"/>
-      <c r="U321" s="9" t="s">
+      <c r="U321" s="79" t="s">
         <v>1615</v>
       </c>
-      <c r="V321" s="9" t="s">
+      <c r="V321" s="79" t="s">
         <v>1614</v>
       </c>
     </row>
@@ -21573,10 +21854,10 @@
       <c r="P322" s="40"/>
       <c r="Q322" s="40"/>
       <c r="R322" s="40"/>
-      <c r="U322" s="9" t="s">
+      <c r="U322" s="79" t="s">
         <v>1616</v>
       </c>
-      <c r="V322" s="9" t="s">
+      <c r="V322" s="79" t="s">
         <v>1614</v>
       </c>
     </row>
@@ -21620,10 +21901,10 @@
       <c r="P323" s="40"/>
       <c r="Q323" s="40"/>
       <c r="R323" s="40"/>
-      <c r="U323" s="9" t="s">
+      <c r="U323" s="79" t="s">
         <v>1617</v>
       </c>
-      <c r="V323" s="9" t="s">
+      <c r="V323" s="79" t="s">
         <v>1614</v>
       </c>
     </row>
@@ -21667,10 +21948,10 @@
       <c r="P324" s="40"/>
       <c r="Q324" s="40"/>
       <c r="R324" s="40"/>
-      <c r="U324" s="9" t="s">
+      <c r="U324" s="79" t="s">
         <v>1618</v>
       </c>
-      <c r="V324" s="9" t="s">
+      <c r="V324" s="79" t="s">
         <v>1619</v>
       </c>
     </row>
@@ -21714,10 +21995,10 @@
       <c r="P325" s="40"/>
       <c r="Q325" s="40"/>
       <c r="R325" s="40"/>
-      <c r="U325" s="9" t="s">
+      <c r="U325" s="79" t="s">
         <v>1620</v>
       </c>
-      <c r="V325" s="9" t="s">
+      <c r="V325" s="79" t="s">
         <v>1619</v>
       </c>
     </row>
@@ -21761,10 +22042,10 @@
       <c r="P326" s="40"/>
       <c r="Q326" s="40"/>
       <c r="R326" s="40"/>
-      <c r="U326" s="9" t="s">
+      <c r="U326" s="79" t="s">
         <v>1621</v>
       </c>
-      <c r="V326" s="9" t="s">
+      <c r="V326" s="79" t="s">
         <v>1622</v>
       </c>
     </row>
@@ -21808,10 +22089,10 @@
       <c r="P327" s="40"/>
       <c r="Q327" s="40"/>
       <c r="R327" s="40"/>
-      <c r="U327" s="9" t="s">
+      <c r="U327" s="79" t="s">
         <v>1623</v>
       </c>
-      <c r="V327" s="9" t="s">
+      <c r="V327" s="79" t="s">
         <v>1624</v>
       </c>
     </row>
@@ -21855,10 +22136,10 @@
       <c r="P328" s="40"/>
       <c r="Q328" s="40"/>
       <c r="R328" s="40"/>
-      <c r="U328" s="9" t="s">
+      <c r="U328" s="79" t="s">
         <v>1625</v>
       </c>
-      <c r="V328" s="9" t="s">
+      <c r="V328" s="79" t="s">
         <v>1624</v>
       </c>
     </row>
@@ -21902,10 +22183,10 @@
       <c r="P329" s="40"/>
       <c r="Q329" s="40"/>
       <c r="R329" s="40"/>
-      <c r="U329" s="9" t="s">
+      <c r="U329" s="79" t="s">
         <v>1626</v>
       </c>
-      <c r="V329" s="9" t="s">
+      <c r="V329" s="79" t="s">
         <v>1627</v>
       </c>
     </row>
@@ -21949,10 +22230,10 @@
       <c r="P330" s="40"/>
       <c r="Q330" s="40"/>
       <c r="R330" s="40"/>
-      <c r="U330" s="9" t="s">
+      <c r="U330" s="79" t="s">
         <v>1628</v>
       </c>
-      <c r="V330" s="9" t="s">
+      <c r="V330" s="79" t="s">
         <v>1627</v>
       </c>
     </row>
@@ -21996,10 +22277,10 @@
       <c r="P331" s="40"/>
       <c r="Q331" s="40"/>
       <c r="R331" s="40"/>
-      <c r="U331" s="9" t="s">
+      <c r="U331" s="79" t="s">
         <v>1629</v>
       </c>
-      <c r="V331" s="9" t="s">
+      <c r="V331" s="79" t="s">
         <v>1627</v>
       </c>
     </row>
@@ -22046,8 +22327,12 @@
       <c r="S332" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U332" s="10"/>
-      <c r="V332" s="10"/>
+      <c r="U332" s="84" t="s">
+        <v>1927</v>
+      </c>
+      <c r="V332" s="84" t="s">
+        <v>1928</v>
+      </c>
     </row>
     <row r="333" spans="1:22" ht="30" customHeight="1">
       <c r="A333" s="43" t="s">
@@ -22092,8 +22377,12 @@
       <c r="S333" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U333" s="10"/>
-      <c r="V333" s="10"/>
+      <c r="U333" s="83" t="s">
+        <v>1905</v>
+      </c>
+      <c r="V333" s="83" t="s">
+        <v>1561</v>
+      </c>
     </row>
     <row r="334" spans="1:22" ht="30" customHeight="1">
       <c r="A334" s="43" t="s">
@@ -22138,8 +22427,12 @@
       <c r="S334" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U334" s="10"/>
-      <c r="V334" s="10"/>
+      <c r="U334" s="83" t="s">
+        <v>1906</v>
+      </c>
+      <c r="V334" s="83" t="s">
+        <v>1601</v>
+      </c>
     </row>
     <row r="335" spans="1:22" ht="15" customHeight="1">
       <c r="A335" s="43"/>
@@ -22161,8 +22454,8 @@
       <c r="Q335" s="40"/>
       <c r="R335" s="40"/>
       <c r="S335" s="39"/>
-      <c r="U335" s="10"/>
-      <c r="V335" s="10"/>
+      <c r="U335" s="81"/>
+      <c r="V335" s="81"/>
     </row>
     <row r="336" spans="1:22" ht="30" customHeight="1">
       <c r="A336" s="43">
@@ -22203,10 +22496,10 @@
       <c r="P336" s="40"/>
       <c r="Q336" s="40"/>
       <c r="R336" s="40"/>
-      <c r="U336" s="9" t="s">
+      <c r="U336" s="79" t="s">
         <v>1630</v>
       </c>
-      <c r="V336" s="9" t="s">
+      <c r="V336" s="79" t="s">
         <v>1631</v>
       </c>
     </row>
@@ -22250,10 +22543,10 @@
       <c r="P337" s="40"/>
       <c r="Q337" s="40"/>
       <c r="R337" s="40"/>
-      <c r="U337" s="9" t="s">
+      <c r="U337" s="79" t="s">
         <v>1632</v>
       </c>
-      <c r="V337" s="9" t="s">
+      <c r="V337" s="79" t="s">
         <v>1631</v>
       </c>
     </row>
@@ -22297,10 +22590,10 @@
       <c r="P338" s="40"/>
       <c r="Q338" s="40"/>
       <c r="R338" s="40"/>
-      <c r="U338" s="9" t="s">
+      <c r="U338" s="79" t="s">
         <v>1633</v>
       </c>
-      <c r="V338" s="9" t="s">
+      <c r="V338" s="79" t="s">
         <v>1634</v>
       </c>
     </row>
@@ -22344,10 +22637,10 @@
       <c r="P339" s="40"/>
       <c r="Q339" s="40"/>
       <c r="R339" s="40"/>
-      <c r="U339" s="9" t="s">
+      <c r="U339" s="79" t="s">
         <v>1635</v>
       </c>
-      <c r="V339" s="9" t="s">
+      <c r="V339" s="79" t="s">
         <v>1634</v>
       </c>
     </row>
@@ -22391,10 +22684,10 @@
       <c r="P340" s="40"/>
       <c r="Q340" s="40"/>
       <c r="R340" s="40"/>
-      <c r="U340" s="9" t="s">
+      <c r="U340" s="79" t="s">
         <v>1636</v>
       </c>
-      <c r="V340" s="9" t="s">
+      <c r="V340" s="79" t="s">
         <v>1637</v>
       </c>
     </row>
@@ -22438,10 +22731,10 @@
       <c r="P341" s="40"/>
       <c r="Q341" s="40"/>
       <c r="R341" s="40"/>
-      <c r="U341" s="9" t="s">
+      <c r="U341" s="79" t="s">
         <v>1638</v>
       </c>
-      <c r="V341" s="9" t="s">
+      <c r="V341" s="79" t="s">
         <v>1639</v>
       </c>
     </row>
@@ -22485,10 +22778,10 @@
       <c r="P342" s="40"/>
       <c r="Q342" s="40"/>
       <c r="R342" s="40"/>
-      <c r="U342" s="9" t="s">
+      <c r="U342" s="79" t="s">
         <v>1640</v>
       </c>
-      <c r="V342" s="9" t="s">
+      <c r="V342" s="79" t="s">
         <v>1639</v>
       </c>
     </row>
@@ -22532,10 +22825,10 @@
       <c r="P343" s="40"/>
       <c r="Q343" s="40"/>
       <c r="R343" s="40"/>
-      <c r="U343" s="9" t="s">
+      <c r="U343" s="79" t="s">
         <v>1641</v>
       </c>
-      <c r="V343" s="9" t="s">
+      <c r="V343" s="79" t="s">
         <v>1639</v>
       </c>
     </row>
@@ -22579,10 +22872,10 @@
       <c r="P344" s="40"/>
       <c r="Q344" s="40"/>
       <c r="R344" s="40"/>
-      <c r="U344" s="9" t="s">
+      <c r="U344" s="79" t="s">
         <v>1642</v>
       </c>
-      <c r="V344" s="9" t="s">
+      <c r="V344" s="79" t="s">
         <v>1639</v>
       </c>
     </row>
@@ -22626,10 +22919,10 @@
       <c r="P345" s="40"/>
       <c r="Q345" s="40"/>
       <c r="R345" s="40"/>
-      <c r="U345" s="9" t="s">
+      <c r="U345" s="79" t="s">
         <v>1643</v>
       </c>
-      <c r="V345" s="9" t="s">
+      <c r="V345" s="79" t="s">
         <v>1644</v>
       </c>
     </row>
@@ -22673,10 +22966,10 @@
       <c r="P346" s="40"/>
       <c r="Q346" s="40"/>
       <c r="R346" s="40"/>
-      <c r="U346" s="9" t="s">
+      <c r="U346" s="79" t="s">
         <v>1645</v>
       </c>
-      <c r="V346" s="9" t="s">
+      <c r="V346" s="79" t="s">
         <v>1644</v>
       </c>
     </row>
@@ -22720,10 +23013,10 @@
       <c r="P347" s="40"/>
       <c r="Q347" s="40"/>
       <c r="R347" s="40"/>
-      <c r="U347" s="9" t="s">
+      <c r="U347" s="79" t="s">
         <v>1646</v>
       </c>
-      <c r="V347" s="9" t="s">
+      <c r="V347" s="79" t="s">
         <v>1644</v>
       </c>
     </row>
@@ -22767,10 +23060,10 @@
       <c r="P348" s="40"/>
       <c r="Q348" s="40"/>
       <c r="R348" s="40"/>
-      <c r="U348" s="9" t="s">
+      <c r="U348" s="79" t="s">
         <v>1647</v>
       </c>
-      <c r="V348" s="9" t="s">
+      <c r="V348" s="79" t="s">
         <v>1648</v>
       </c>
     </row>
@@ -22814,10 +23107,10 @@
       <c r="P349" s="40"/>
       <c r="Q349" s="40"/>
       <c r="R349" s="40"/>
-      <c r="U349" s="9" t="s">
+      <c r="U349" s="79" t="s">
         <v>1649</v>
       </c>
-      <c r="V349" s="9" t="s">
+      <c r="V349" s="79" t="s">
         <v>1648</v>
       </c>
     </row>
@@ -22861,10 +23154,10 @@
       <c r="P350" s="40"/>
       <c r="Q350" s="40"/>
       <c r="R350" s="40"/>
-      <c r="U350" s="9" t="s">
+      <c r="U350" s="79" t="s">
         <v>1650</v>
       </c>
-      <c r="V350" s="9" t="s">
+      <c r="V350" s="79" t="s">
         <v>1651</v>
       </c>
     </row>
@@ -22908,10 +23201,10 @@
       <c r="P351" s="40"/>
       <c r="Q351" s="40"/>
       <c r="R351" s="40"/>
-      <c r="U351" s="9" t="s">
+      <c r="U351" s="79" t="s">
         <v>1652</v>
       </c>
-      <c r="V351" s="9" t="s">
+      <c r="V351" s="79" t="s">
         <v>1651</v>
       </c>
     </row>
@@ -22955,10 +23248,10 @@
       <c r="P352" s="40"/>
       <c r="Q352" s="40"/>
       <c r="R352" s="40"/>
-      <c r="U352" s="9" t="s">
+      <c r="U352" s="79" t="s">
         <v>1653</v>
       </c>
-      <c r="V352" s="9" t="s">
+      <c r="V352" s="79" t="s">
         <v>1651</v>
       </c>
     </row>
@@ -23002,10 +23295,10 @@
       <c r="P353" s="40"/>
       <c r="Q353" s="40"/>
       <c r="R353" s="40"/>
-      <c r="U353" s="9" t="s">
+      <c r="U353" s="79" t="s">
         <v>1654</v>
       </c>
-      <c r="V353" s="9" t="s">
+      <c r="V353" s="79" t="s">
         <v>1651</v>
       </c>
     </row>
@@ -23049,10 +23342,10 @@
       <c r="P354" s="40"/>
       <c r="Q354" s="40"/>
       <c r="R354" s="40"/>
-      <c r="U354" s="9" t="s">
+      <c r="U354" s="79" t="s">
         <v>1655</v>
       </c>
-      <c r="V354" s="9" t="s">
+      <c r="V354" s="79" t="s">
         <v>1656</v>
       </c>
     </row>
@@ -23096,10 +23389,10 @@
       <c r="P355" s="40"/>
       <c r="Q355" s="40"/>
       <c r="R355" s="40"/>
-      <c r="U355" s="9" t="s">
+      <c r="U355" s="79" t="s">
         <v>1657</v>
       </c>
-      <c r="V355" s="9" t="s">
+      <c r="V355" s="79" t="s">
         <v>1656</v>
       </c>
     </row>
@@ -23143,10 +23436,10 @@
       <c r="P356" s="40"/>
       <c r="Q356" s="40"/>
       <c r="R356" s="40"/>
-      <c r="U356" s="9" t="s">
+      <c r="U356" s="79" t="s">
         <v>1658</v>
       </c>
-      <c r="V356" s="9" t="s">
+      <c r="V356" s="79" t="s">
         <v>1656</v>
       </c>
     </row>
@@ -23190,10 +23483,10 @@
       <c r="P357" s="40"/>
       <c r="Q357" s="40"/>
       <c r="R357" s="40"/>
-      <c r="U357" s="9" t="s">
+      <c r="U357" s="79" t="s">
         <v>1659</v>
       </c>
-      <c r="V357" s="9" t="s">
+      <c r="V357" s="79" t="s">
         <v>1660</v>
       </c>
     </row>
@@ -23237,10 +23530,10 @@
       <c r="P358" s="40"/>
       <c r="Q358" s="40"/>
       <c r="R358" s="40"/>
-      <c r="U358" s="9" t="s">
+      <c r="U358" s="79" t="s">
         <v>1661</v>
       </c>
-      <c r="V358" s="9" t="s">
+      <c r="V358" s="79" t="s">
         <v>1662</v>
       </c>
     </row>
@@ -23284,10 +23577,10 @@
       <c r="P359" s="40"/>
       <c r="Q359" s="40"/>
       <c r="R359" s="40"/>
-      <c r="U359" s="9" t="s">
+      <c r="U359" s="79" t="s">
         <v>1663</v>
       </c>
-      <c r="V359" s="9" t="s">
+      <c r="V359" s="79" t="s">
         <v>1662</v>
       </c>
     </row>
@@ -23331,10 +23624,10 @@
       <c r="P360" s="40"/>
       <c r="Q360" s="40"/>
       <c r="R360" s="40"/>
-      <c r="U360" s="9" t="s">
+      <c r="U360" s="79" t="s">
         <v>1664</v>
       </c>
-      <c r="V360" s="9" t="s">
+      <c r="V360" s="79" t="s">
         <v>1665</v>
       </c>
     </row>
@@ -23378,10 +23671,10 @@
       <c r="P361" s="40"/>
       <c r="Q361" s="40"/>
       <c r="R361" s="40"/>
-      <c r="U361" s="9" t="s">
+      <c r="U361" s="79" t="s">
         <v>1666</v>
       </c>
-      <c r="V361" s="9" t="s">
+      <c r="V361" s="79" t="s">
         <v>1665</v>
       </c>
     </row>
@@ -23425,10 +23718,10 @@
       <c r="P362" s="40"/>
       <c r="Q362" s="40"/>
       <c r="R362" s="40"/>
-      <c r="U362" s="9" t="s">
+      <c r="U362" s="79" t="s">
         <v>1667</v>
       </c>
-      <c r="V362" s="9" t="s">
+      <c r="V362" s="79" t="s">
         <v>1668</v>
       </c>
     </row>
@@ -23472,10 +23765,10 @@
       <c r="P363" s="40"/>
       <c r="Q363" s="40"/>
       <c r="R363" s="40"/>
-      <c r="U363" s="9" t="s">
+      <c r="U363" s="79" t="s">
         <v>1669</v>
       </c>
-      <c r="V363" s="9" t="s">
+      <c r="V363" s="79" t="s">
         <v>1668</v>
       </c>
     </row>
@@ -23519,10 +23812,10 @@
       <c r="P364" s="40"/>
       <c r="Q364" s="40"/>
       <c r="R364" s="40"/>
-      <c r="U364" s="9" t="s">
+      <c r="U364" s="79" t="s">
         <v>1670</v>
       </c>
-      <c r="V364" s="9" t="s">
+      <c r="V364" s="79" t="s">
         <v>1668</v>
       </c>
     </row>
@@ -23566,10 +23859,10 @@
       <c r="P365" s="40"/>
       <c r="Q365" s="40"/>
       <c r="R365" s="40"/>
-      <c r="U365" s="9" t="s">
+      <c r="U365" s="79" t="s">
         <v>1671</v>
       </c>
-      <c r="V365" s="9" t="s">
+      <c r="V365" s="79" t="s">
         <v>1672</v>
       </c>
     </row>
@@ -23613,10 +23906,10 @@
       <c r="P366" s="40"/>
       <c r="Q366" s="40"/>
       <c r="R366" s="40"/>
-      <c r="U366" s="9" t="s">
+      <c r="U366" s="79" t="s">
         <v>1673</v>
       </c>
-      <c r="V366" s="9" t="s">
+      <c r="V366" s="79" t="s">
         <v>1672</v>
       </c>
     </row>
@@ -23660,10 +23953,10 @@
       <c r="P367" s="40"/>
       <c r="Q367" s="40"/>
       <c r="R367" s="40"/>
-      <c r="U367" s="9" t="s">
+      <c r="U367" s="79" t="s">
         <v>1674</v>
       </c>
-      <c r="V367" s="9" t="s">
+      <c r="V367" s="79" t="s">
         <v>1675</v>
       </c>
     </row>
@@ -23707,10 +24000,10 @@
       <c r="P368" s="40"/>
       <c r="Q368" s="40"/>
       <c r="R368" s="40"/>
-      <c r="U368" s="9" t="s">
+      <c r="U368" s="79" t="s">
         <v>1676</v>
       </c>
-      <c r="V368" s="9" t="s">
+      <c r="V368" s="79" t="s">
         <v>1675</v>
       </c>
     </row>
@@ -23754,10 +24047,10 @@
       <c r="P369" s="40"/>
       <c r="Q369" s="40"/>
       <c r="R369" s="40"/>
-      <c r="U369" s="9" t="s">
+      <c r="U369" s="79" t="s">
         <v>1677</v>
       </c>
-      <c r="V369" s="9" t="s">
+      <c r="V369" s="79" t="s">
         <v>1678</v>
       </c>
     </row>
@@ -23801,10 +24094,10 @@
       <c r="P370" s="40"/>
       <c r="Q370" s="40"/>
       <c r="R370" s="40"/>
-      <c r="U370" s="9" t="s">
+      <c r="U370" s="79" t="s">
         <v>1679</v>
       </c>
-      <c r="V370" s="9" t="s">
+      <c r="V370" s="79" t="s">
         <v>1678</v>
       </c>
     </row>
@@ -23848,10 +24141,10 @@
       <c r="P371" s="40"/>
       <c r="Q371" s="40"/>
       <c r="R371" s="40"/>
-      <c r="U371" s="9" t="s">
+      <c r="U371" s="79" t="s">
         <v>1680</v>
       </c>
-      <c r="V371" s="9" t="s">
+      <c r="V371" s="79" t="s">
         <v>1678</v>
       </c>
     </row>
@@ -23895,10 +24188,10 @@
       <c r="P372" s="40"/>
       <c r="Q372" s="40"/>
       <c r="R372" s="40"/>
-      <c r="U372" s="9" t="s">
+      <c r="U372" s="79" t="s">
         <v>1681</v>
       </c>
-      <c r="V372" s="9" t="s">
+      <c r="V372" s="79" t="s">
         <v>1682</v>
       </c>
     </row>
@@ -23942,10 +24235,10 @@
       <c r="P373" s="40"/>
       <c r="Q373" s="40"/>
       <c r="R373" s="40"/>
-      <c r="U373" s="9" t="s">
+      <c r="U373" s="79" t="s">
         <v>1683</v>
       </c>
-      <c r="V373" s="9" t="s">
+      <c r="V373" s="79" t="s">
         <v>1682</v>
       </c>
     </row>
@@ -23989,10 +24282,10 @@
       <c r="P374" s="40"/>
       <c r="Q374" s="40"/>
       <c r="R374" s="40"/>
-      <c r="U374" s="9" t="s">
+      <c r="U374" s="79" t="s">
         <v>1684</v>
       </c>
-      <c r="V374" s="9" t="s">
+      <c r="V374" s="79" t="s">
         <v>1682</v>
       </c>
     </row>
@@ -24036,10 +24329,10 @@
       <c r="P375" s="40"/>
       <c r="Q375" s="40"/>
       <c r="R375" s="40"/>
-      <c r="U375" s="9" t="s">
+      <c r="U375" s="79" t="s">
         <v>1685</v>
       </c>
-      <c r="V375" s="9" t="s">
+      <c r="V375" s="79" t="s">
         <v>1686</v>
       </c>
     </row>
@@ -24083,10 +24376,10 @@
       <c r="P376" s="40"/>
       <c r="Q376" s="40"/>
       <c r="R376" s="40"/>
-      <c r="U376" s="9" t="s">
+      <c r="U376" s="79" t="s">
         <v>1687</v>
       </c>
-      <c r="V376" s="9" t="s">
+      <c r="V376" s="79" t="s">
         <v>1686</v>
       </c>
     </row>
@@ -24130,10 +24423,10 @@
       <c r="P377" s="40"/>
       <c r="Q377" s="40"/>
       <c r="R377" s="40"/>
-      <c r="U377" s="9" t="s">
+      <c r="U377" s="79" t="s">
         <v>1688</v>
       </c>
-      <c r="V377" s="9" t="s">
+      <c r="V377" s="79" t="s">
         <v>1689</v>
       </c>
     </row>
@@ -24177,10 +24470,10 @@
       <c r="P378" s="40"/>
       <c r="Q378" s="40"/>
       <c r="R378" s="40"/>
-      <c r="U378" s="9" t="s">
+      <c r="U378" s="79" t="s">
         <v>1690</v>
       </c>
-      <c r="V378" s="9" t="s">
+      <c r="V378" s="79" t="s">
         <v>1689</v>
       </c>
     </row>
@@ -24224,10 +24517,10 @@
       <c r="P379" s="40"/>
       <c r="Q379" s="40"/>
       <c r="R379" s="40"/>
-      <c r="U379" s="9" t="s">
+      <c r="U379" s="79" t="s">
         <v>1691</v>
       </c>
-      <c r="V379" s="9" t="s">
+      <c r="V379" s="79" t="s">
         <v>1689</v>
       </c>
     </row>
@@ -24271,10 +24564,10 @@
       <c r="P380" s="40"/>
       <c r="Q380" s="40"/>
       <c r="R380" s="40"/>
-      <c r="U380" s="9" t="s">
+      <c r="U380" s="79" t="s">
         <v>1692</v>
       </c>
-      <c r="V380" s="9" t="s">
+      <c r="V380" s="79" t="s">
         <v>1689</v>
       </c>
     </row>
@@ -24318,10 +24611,10 @@
       <c r="P381" s="40"/>
       <c r="Q381" s="40"/>
       <c r="R381" s="40"/>
-      <c r="U381" s="9" t="s">
+      <c r="U381" s="79" t="s">
         <v>1693</v>
       </c>
-      <c r="V381" s="9" t="s">
+      <c r="V381" s="79" t="s">
         <v>1689</v>
       </c>
     </row>
@@ -24368,8 +24661,12 @@
       <c r="S382" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U382" s="10"/>
-      <c r="V382" s="10"/>
+      <c r="U382" s="80" t="s">
+        <v>1930</v>
+      </c>
+      <c r="V382" s="80" t="s">
+        <v>1929</v>
+      </c>
     </row>
     <row r="383" spans="1:22" ht="15" customHeight="1">
       <c r="A383" s="43"/>
@@ -24391,8 +24688,8 @@
       <c r="Q383" s="40"/>
       <c r="R383" s="40"/>
       <c r="S383" s="39"/>
-      <c r="U383" s="10"/>
-      <c r="V383" s="10"/>
+      <c r="U383" s="81"/>
+      <c r="V383" s="81"/>
     </row>
     <row r="384" spans="1:22" ht="30" customHeight="1">
       <c r="A384" s="43" t="s">
@@ -24433,10 +24730,10 @@
       <c r="P384" s="40"/>
       <c r="Q384" s="40"/>
       <c r="R384" s="40"/>
-      <c r="U384" s="9" t="s">
+      <c r="U384" s="79" t="s">
         <v>1694</v>
       </c>
-      <c r="V384" s="9" t="s">
+      <c r="V384" s="79" t="s">
         <v>1695</v>
       </c>
     </row>
@@ -24480,10 +24777,10 @@
       <c r="P385" s="40"/>
       <c r="Q385" s="40"/>
       <c r="R385" s="40"/>
-      <c r="U385" s="9" t="s">
+      <c r="U385" s="79" t="s">
         <v>1696</v>
       </c>
-      <c r="V385" s="9" t="s">
+      <c r="V385" s="79" t="s">
         <v>1695</v>
       </c>
     </row>
@@ -24527,10 +24824,10 @@
       <c r="P386" s="40"/>
       <c r="Q386" s="40"/>
       <c r="R386" s="40"/>
-      <c r="U386" s="9" t="s">
+      <c r="U386" s="79" t="s">
         <v>1697</v>
       </c>
-      <c r="V386" s="9" t="s">
+      <c r="V386" s="79" t="s">
         <v>1698</v>
       </c>
     </row>
@@ -24574,10 +24871,10 @@
       <c r="P387" s="40"/>
       <c r="Q387" s="40"/>
       <c r="R387" s="40"/>
-      <c r="U387" s="9" t="s">
+      <c r="U387" s="79" t="s">
         <v>1699</v>
       </c>
-      <c r="V387" s="9" t="s">
+      <c r="V387" s="79" t="s">
         <v>1698</v>
       </c>
     </row>
@@ -24621,10 +24918,10 @@
       <c r="P388" s="40"/>
       <c r="Q388" s="40"/>
       <c r="R388" s="40"/>
-      <c r="U388" s="9" t="s">
+      <c r="U388" s="79" t="s">
         <v>1700</v>
       </c>
-      <c r="V388" s="9" t="s">
+      <c r="V388" s="79" t="s">
         <v>1698</v>
       </c>
     </row>
@@ -24668,10 +24965,10 @@
       <c r="P389" s="40"/>
       <c r="Q389" s="40"/>
       <c r="R389" s="40"/>
-      <c r="U389" s="9" t="s">
+      <c r="U389" s="79" t="s">
         <v>1701</v>
       </c>
-      <c r="V389" s="9" t="s">
+      <c r="V389" s="79" t="s">
         <v>1702</v>
       </c>
     </row>
@@ -24715,10 +25012,10 @@
       <c r="P390" s="40"/>
       <c r="Q390" s="40"/>
       <c r="R390" s="40"/>
-      <c r="U390" s="9" t="s">
+      <c r="U390" s="79" t="s">
         <v>1703</v>
       </c>
-      <c r="V390" s="9" t="s">
+      <c r="V390" s="79" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -24762,10 +25059,10 @@
       <c r="P391" s="40"/>
       <c r="Q391" s="40"/>
       <c r="R391" s="40"/>
-      <c r="U391" s="9" t="s">
+      <c r="U391" s="79" t="s">
         <v>1705</v>
       </c>
-      <c r="V391" s="9" t="s">
+      <c r="V391" s="79" t="s">
         <v>1704</v>
       </c>
     </row>
@@ -24809,10 +25106,10 @@
       <c r="P392" s="40"/>
       <c r="Q392" s="40"/>
       <c r="R392" s="40"/>
-      <c r="U392" s="9" t="s">
+      <c r="U392" s="79" t="s">
         <v>1706</v>
       </c>
-      <c r="V392" s="9" t="s">
+      <c r="V392" s="79" t="s">
         <v>1707</v>
       </c>
     </row>
@@ -24856,10 +25153,10 @@
       <c r="P393" s="40"/>
       <c r="Q393" s="40"/>
       <c r="R393" s="40"/>
-      <c r="U393" s="9" t="s">
+      <c r="U393" s="79" t="s">
         <v>1708</v>
       </c>
-      <c r="V393" s="9" t="s">
+      <c r="V393" s="79" t="s">
         <v>1707</v>
       </c>
     </row>
@@ -24903,10 +25200,10 @@
       <c r="P394" s="40"/>
       <c r="Q394" s="40"/>
       <c r="R394" s="40"/>
-      <c r="U394" s="9" t="s">
+      <c r="U394" s="79" t="s">
         <v>1709</v>
       </c>
-      <c r="V394" s="9" t="s">
+      <c r="V394" s="79" t="s">
         <v>1710</v>
       </c>
     </row>
@@ -24950,10 +25247,10 @@
       <c r="P395" s="40"/>
       <c r="Q395" s="40"/>
       <c r="R395" s="40"/>
-      <c r="U395" s="9" t="s">
+      <c r="U395" s="79" t="s">
         <v>1711</v>
       </c>
-      <c r="V395" s="9" t="s">
+      <c r="V395" s="79" t="s">
         <v>1710</v>
       </c>
     </row>
@@ -24997,10 +25294,10 @@
       <c r="P396" s="40"/>
       <c r="Q396" s="40"/>
       <c r="R396" s="40"/>
-      <c r="U396" s="9" t="s">
+      <c r="U396" s="79" t="s">
         <v>1712</v>
       </c>
-      <c r="V396" s="9" t="s">
+      <c r="V396" s="79" t="s">
         <v>1713</v>
       </c>
     </row>
@@ -25044,10 +25341,10 @@
       <c r="P397" s="40"/>
       <c r="Q397" s="40"/>
       <c r="R397" s="40"/>
-      <c r="U397" s="9" t="s">
+      <c r="U397" s="79" t="s">
         <v>1714</v>
       </c>
-      <c r="V397" s="9" t="s">
+      <c r="V397" s="79" t="s">
         <v>1713</v>
       </c>
     </row>
@@ -25091,10 +25388,10 @@
       <c r="P398" s="40"/>
       <c r="Q398" s="40"/>
       <c r="R398" s="40"/>
-      <c r="U398" s="9" t="s">
+      <c r="U398" s="79" t="s">
         <v>1715</v>
       </c>
-      <c r="V398" s="9" t="s">
+      <c r="V398" s="79" t="s">
         <v>1713</v>
       </c>
     </row>
@@ -25138,10 +25435,10 @@
       <c r="P399" s="40"/>
       <c r="Q399" s="40"/>
       <c r="R399" s="40"/>
-      <c r="U399" s="9" t="s">
+      <c r="U399" s="79" t="s">
         <v>1716</v>
       </c>
-      <c r="V399" s="9" t="s">
+      <c r="V399" s="79" t="s">
         <v>1717</v>
       </c>
     </row>
@@ -25185,10 +25482,10 @@
       <c r="P400" s="40"/>
       <c r="Q400" s="40"/>
       <c r="R400" s="40"/>
-      <c r="U400" s="9" t="s">
+      <c r="U400" s="79" t="s">
         <v>1718</v>
       </c>
-      <c r="V400" s="9" t="s">
+      <c r="V400" s="79" t="s">
         <v>1719</v>
       </c>
     </row>
@@ -25232,10 +25529,10 @@
       <c r="P401" s="40"/>
       <c r="Q401" s="40"/>
       <c r="R401" s="40"/>
-      <c r="U401" s="9" t="s">
+      <c r="U401" s="79" t="s">
         <v>1720</v>
       </c>
-      <c r="V401" s="9" t="s">
+      <c r="V401" s="79" t="s">
         <v>1719</v>
       </c>
     </row>
@@ -25279,10 +25576,10 @@
       <c r="P402" s="40"/>
       <c r="Q402" s="40"/>
       <c r="R402" s="40"/>
-      <c r="U402" s="9" t="s">
+      <c r="U402" s="79" t="s">
         <v>1721</v>
       </c>
-      <c r="V402" s="9" t="s">
+      <c r="V402" s="79" t="s">
         <v>1719</v>
       </c>
     </row>
@@ -25326,10 +25623,10 @@
       <c r="P403" s="40"/>
       <c r="Q403" s="40"/>
       <c r="R403" s="40"/>
-      <c r="U403" s="9" t="s">
+      <c r="U403" s="79" t="s">
         <v>1722</v>
       </c>
-      <c r="V403" s="9" t="s">
+      <c r="V403" s="79" t="s">
         <v>1719</v>
       </c>
     </row>
@@ -25373,10 +25670,10 @@
       <c r="P404" s="40"/>
       <c r="Q404" s="40"/>
       <c r="R404" s="40"/>
-      <c r="U404" s="9" t="s">
+      <c r="U404" s="79" t="s">
         <v>1723</v>
       </c>
-      <c r="V404" s="9" t="s">
+      <c r="V404" s="79" t="s">
         <v>1724</v>
       </c>
     </row>
@@ -25420,10 +25717,10 @@
       <c r="P405" s="40"/>
       <c r="Q405" s="40"/>
       <c r="R405" s="40"/>
-      <c r="U405" s="9" t="s">
+      <c r="U405" s="79" t="s">
         <v>1725</v>
       </c>
-      <c r="V405" s="9" t="s">
+      <c r="V405" s="79" t="s">
         <v>1724</v>
       </c>
     </row>
@@ -25467,10 +25764,10 @@
       <c r="P406" s="40"/>
       <c r="Q406" s="40"/>
       <c r="R406" s="40"/>
-      <c r="U406" s="9" t="s">
+      <c r="U406" s="79" t="s">
         <v>1726</v>
       </c>
-      <c r="V406" s="9" t="s">
+      <c r="V406" s="79" t="s">
         <v>1724</v>
       </c>
     </row>
@@ -25514,10 +25811,10 @@
       <c r="P407" s="40"/>
       <c r="Q407" s="40"/>
       <c r="R407" s="40"/>
-      <c r="U407" s="9" t="s">
+      <c r="U407" s="79" t="s">
         <v>1727</v>
       </c>
-      <c r="V407" s="9" t="s">
+      <c r="V407" s="79" t="s">
         <v>1724</v>
       </c>
     </row>
@@ -25561,10 +25858,10 @@
       <c r="P408" s="40"/>
       <c r="Q408" s="40"/>
       <c r="R408" s="40"/>
-      <c r="U408" s="9" t="s">
+      <c r="U408" s="79" t="s">
         <v>1728</v>
       </c>
-      <c r="V408" s="9" t="s">
+      <c r="V408" s="79" t="s">
         <v>1729</v>
       </c>
     </row>
@@ -25608,10 +25905,10 @@
       <c r="P409" s="40"/>
       <c r="Q409" s="40"/>
       <c r="R409" s="40"/>
-      <c r="U409" s="9" t="s">
+      <c r="U409" s="79" t="s">
         <v>1730</v>
       </c>
-      <c r="V409" s="9" t="s">
+      <c r="V409" s="79" t="s">
         <v>1729</v>
       </c>
     </row>
@@ -25655,10 +25952,10 @@
       <c r="P410" s="40"/>
       <c r="Q410" s="40"/>
       <c r="R410" s="40"/>
-      <c r="U410" s="9" t="s">
+      <c r="U410" s="79" t="s">
         <v>1731</v>
       </c>
-      <c r="V410" s="9" t="s">
+      <c r="V410" s="79" t="s">
         <v>1729</v>
       </c>
     </row>
@@ -25702,10 +25999,10 @@
       <c r="P411" s="40"/>
       <c r="Q411" s="40"/>
       <c r="R411" s="40"/>
-      <c r="U411" s="9" t="s">
+      <c r="U411" s="79" t="s">
         <v>1732</v>
       </c>
-      <c r="V411" s="9" t="s">
+      <c r="V411" s="79" t="s">
         <v>1733</v>
       </c>
     </row>
@@ -25749,10 +26046,10 @@
       <c r="P412" s="40"/>
       <c r="Q412" s="40"/>
       <c r="R412" s="40"/>
-      <c r="U412" s="9" t="s">
+      <c r="U412" s="79" t="s">
         <v>1734</v>
       </c>
-      <c r="V412" s="9" t="s">
+      <c r="V412" s="79" t="s">
         <v>1733</v>
       </c>
     </row>
@@ -25796,10 +26093,10 @@
       <c r="P413" s="40"/>
       <c r="Q413" s="40"/>
       <c r="R413" s="40"/>
-      <c r="U413" s="9" t="s">
+      <c r="U413" s="79" t="s">
         <v>1735</v>
       </c>
-      <c r="V413" s="9" t="s">
+      <c r="V413" s="79" t="s">
         <v>1736</v>
       </c>
     </row>
@@ -25843,10 +26140,10 @@
       <c r="P414" s="40"/>
       <c r="Q414" s="40"/>
       <c r="R414" s="40"/>
-      <c r="U414" s="9" t="s">
+      <c r="U414" s="79" t="s">
         <v>1737</v>
       </c>
-      <c r="V414" s="9" t="s">
+      <c r="V414" s="79" t="s">
         <v>1738</v>
       </c>
     </row>
@@ -25890,10 +26187,10 @@
       <c r="P415" s="40"/>
       <c r="Q415" s="40"/>
       <c r="R415" s="40"/>
-      <c r="U415" s="9" t="s">
+      <c r="U415" s="79" t="s">
         <v>1739</v>
       </c>
-      <c r="V415" s="9" t="s">
+      <c r="V415" s="79" t="s">
         <v>1738</v>
       </c>
     </row>
@@ -25937,10 +26234,10 @@
       <c r="P416" s="40"/>
       <c r="Q416" s="40"/>
       <c r="R416" s="40"/>
-      <c r="U416" s="9" t="s">
+      <c r="U416" s="79" t="s">
         <v>1740</v>
       </c>
-      <c r="V416" s="9" t="s">
+      <c r="V416" s="79" t="s">
         <v>1741</v>
       </c>
     </row>
@@ -25984,10 +26281,10 @@
       <c r="P417" s="40"/>
       <c r="Q417" s="40"/>
       <c r="R417" s="40"/>
-      <c r="U417" s="9" t="s">
+      <c r="U417" s="79" t="s">
         <v>1742</v>
       </c>
-      <c r="V417" s="9" t="s">
+      <c r="V417" s="79" t="s">
         <v>1743</v>
       </c>
     </row>
@@ -26031,10 +26328,10 @@
       <c r="P418" s="40"/>
       <c r="Q418" s="40"/>
       <c r="R418" s="40"/>
-      <c r="U418" s="9" t="s">
+      <c r="U418" s="79" t="s">
         <v>1744</v>
       </c>
-      <c r="V418" s="9" t="s">
+      <c r="V418" s="79" t="s">
         <v>1743</v>
       </c>
     </row>
@@ -26078,10 +26375,10 @@
       <c r="P419" s="40"/>
       <c r="Q419" s="40"/>
       <c r="R419" s="40"/>
-      <c r="U419" s="9" t="s">
+      <c r="U419" s="79" t="s">
         <v>1745</v>
       </c>
-      <c r="V419" s="9" t="s">
+      <c r="V419" s="79" t="s">
         <v>1743</v>
       </c>
     </row>
@@ -26125,10 +26422,10 @@
       <c r="P420" s="40"/>
       <c r="Q420" s="40"/>
       <c r="R420" s="40"/>
-      <c r="U420" s="9" t="s">
+      <c r="U420" s="79" t="s">
         <v>1746</v>
       </c>
-      <c r="V420" s="9" t="s">
+      <c r="V420" s="79" t="s">
         <v>1743</v>
       </c>
     </row>
@@ -26172,10 +26469,10 @@
       <c r="P421" s="40"/>
       <c r="Q421" s="40"/>
       <c r="R421" s="40"/>
-      <c r="U421" s="9" t="s">
+      <c r="U421" s="79" t="s">
         <v>1747</v>
       </c>
-      <c r="V421" s="9" t="s">
+      <c r="V421" s="79" t="s">
         <v>1743</v>
       </c>
     </row>
@@ -26219,10 +26516,10 @@
       <c r="P422" s="40"/>
       <c r="Q422" s="40"/>
       <c r="R422" s="40"/>
-      <c r="U422" s="9" t="s">
+      <c r="U422" s="79" t="s">
         <v>1748</v>
       </c>
-      <c r="V422" s="9" t="s">
+      <c r="V422" s="79" t="s">
         <v>1749</v>
       </c>
     </row>
@@ -26266,10 +26563,10 @@
       <c r="P423" s="40"/>
       <c r="Q423" s="40"/>
       <c r="R423" s="40"/>
-      <c r="U423" s="9" t="s">
+      <c r="U423" s="79" t="s">
         <v>1750</v>
       </c>
-      <c r="V423" s="9" t="s">
+      <c r="V423" s="79" t="s">
         <v>1749</v>
       </c>
     </row>
@@ -26313,10 +26610,10 @@
       <c r="P424" s="40"/>
       <c r="Q424" s="40"/>
       <c r="R424" s="40"/>
-      <c r="U424" s="9" t="s">
+      <c r="U424" s="79" t="s">
         <v>1751</v>
       </c>
-      <c r="V424" s="9" t="s">
+      <c r="V424" s="79" t="s">
         <v>1752</v>
       </c>
     </row>
@@ -26360,10 +26657,10 @@
       <c r="P425" s="40"/>
       <c r="Q425" s="40"/>
       <c r="R425" s="40"/>
-      <c r="U425" s="9" t="s">
+      <c r="U425" s="79" t="s">
         <v>1753</v>
       </c>
-      <c r="V425" s="9" t="s">
+      <c r="V425" s="79" t="s">
         <v>1752</v>
       </c>
     </row>
@@ -26407,10 +26704,10 @@
       <c r="P426" s="40"/>
       <c r="Q426" s="40"/>
       <c r="R426" s="40"/>
-      <c r="U426" s="9" t="s">
+      <c r="U426" s="79" t="s">
         <v>1754</v>
       </c>
-      <c r="V426" s="9" t="s">
+      <c r="V426" s="79" t="s">
         <v>1752</v>
       </c>
     </row>
@@ -26454,10 +26751,10 @@
       <c r="P427" s="40"/>
       <c r="Q427" s="40"/>
       <c r="R427" s="40"/>
-      <c r="U427" s="9" t="s">
+      <c r="U427" s="79" t="s">
         <v>1755</v>
       </c>
-      <c r="V427" s="9" t="s">
+      <c r="V427" s="79" t="s">
         <v>1756</v>
       </c>
     </row>
@@ -26501,10 +26798,10 @@
       <c r="P428" s="40"/>
       <c r="Q428" s="40"/>
       <c r="R428" s="40"/>
-      <c r="U428" s="9" t="s">
+      <c r="U428" s="79" t="s">
         <v>1757</v>
       </c>
-      <c r="V428" s="9" t="s">
+      <c r="V428" s="79" t="s">
         <v>1756</v>
       </c>
     </row>
@@ -26548,10 +26845,10 @@
       <c r="P429" s="40"/>
       <c r="Q429" s="40"/>
       <c r="R429" s="40"/>
-      <c r="U429" s="9" t="s">
+      <c r="U429" s="79" t="s">
         <v>1758</v>
       </c>
-      <c r="V429" s="9" t="s">
+      <c r="V429" s="79" t="s">
         <v>1759</v>
       </c>
     </row>
@@ -26595,10 +26892,10 @@
       <c r="P430" s="40"/>
       <c r="Q430" s="40"/>
       <c r="R430" s="40"/>
-      <c r="U430" s="9" t="s">
+      <c r="U430" s="79" t="s">
         <v>1760</v>
       </c>
-      <c r="V430" s="9" t="s">
+      <c r="V430" s="79" t="s">
         <v>1759</v>
       </c>
     </row>
@@ -26642,10 +26939,10 @@
       <c r="P431" s="40"/>
       <c r="Q431" s="40"/>
       <c r="R431" s="40"/>
-      <c r="U431" s="9" t="s">
+      <c r="U431" s="79" t="s">
         <v>1761</v>
       </c>
-      <c r="V431" s="9" t="s">
+      <c r="V431" s="79" t="s">
         <v>1762</v>
       </c>
     </row>
@@ -26689,10 +26986,10 @@
       <c r="P432" s="40"/>
       <c r="Q432" s="40"/>
       <c r="R432" s="40"/>
-      <c r="U432" s="9" t="s">
+      <c r="U432" s="79" t="s">
         <v>1763</v>
       </c>
-      <c r="V432" s="9" t="s">
+      <c r="V432" s="79" t="s">
         <v>1762</v>
       </c>
     </row>
@@ -26736,10 +27033,10 @@
       <c r="P433" s="40"/>
       <c r="Q433" s="40"/>
       <c r="R433" s="40"/>
-      <c r="U433" s="9" t="s">
+      <c r="U433" s="79" t="s">
         <v>1764</v>
       </c>
-      <c r="V433" s="9" t="s">
+      <c r="V433" s="79" t="s">
         <v>1765</v>
       </c>
     </row>
@@ -26783,10 +27080,10 @@
       <c r="P434" s="40"/>
       <c r="Q434" s="40"/>
       <c r="R434" s="40"/>
-      <c r="U434" s="9" t="s">
+      <c r="U434" s="79" t="s">
         <v>1766</v>
       </c>
-      <c r="V434" s="9" t="s">
+      <c r="V434" s="79" t="s">
         <v>1765</v>
       </c>
     </row>
@@ -26830,10 +27127,10 @@
       <c r="P435" s="40"/>
       <c r="Q435" s="40"/>
       <c r="R435" s="40"/>
-      <c r="U435" s="9" t="s">
+      <c r="U435" s="79" t="s">
         <v>1767</v>
       </c>
-      <c r="V435" s="9" t="s">
+      <c r="V435" s="79" t="s">
         <v>1768</v>
       </c>
     </row>
@@ -26877,10 +27174,10 @@
       <c r="P436" s="40"/>
       <c r="Q436" s="40"/>
       <c r="R436" s="40"/>
-      <c r="U436" s="9" t="s">
+      <c r="U436" s="79" t="s">
         <v>1769</v>
       </c>
-      <c r="V436" s="9" t="s">
+      <c r="V436" s="79" t="s">
         <v>1768</v>
       </c>
     </row>
@@ -26924,10 +27221,10 @@
       <c r="P437" s="40"/>
       <c r="Q437" s="40"/>
       <c r="R437" s="40"/>
-      <c r="U437" s="9" t="s">
+      <c r="U437" s="79" t="s">
         <v>1770</v>
       </c>
-      <c r="V437" s="9" t="s">
+      <c r="V437" s="79" t="s">
         <v>1771</v>
       </c>
     </row>
@@ -26971,10 +27268,10 @@
       <c r="P438" s="40"/>
       <c r="Q438" s="40"/>
       <c r="R438" s="40"/>
-      <c r="U438" s="9" t="s">
+      <c r="U438" s="79" t="s">
         <v>1772</v>
       </c>
-      <c r="V438" s="9" t="s">
+      <c r="V438" s="79" t="s">
         <v>1771</v>
       </c>
     </row>
@@ -27018,10 +27315,10 @@
       <c r="P439" s="40"/>
       <c r="Q439" s="40"/>
       <c r="R439" s="40"/>
-      <c r="U439" s="9" t="s">
+      <c r="U439" s="79" t="s">
         <v>1773</v>
       </c>
-      <c r="V439" s="9" t="s">
+      <c r="V439" s="79" t="s">
         <v>1771</v>
       </c>
     </row>
@@ -27065,10 +27362,10 @@
       <c r="P440" s="40"/>
       <c r="Q440" s="40"/>
       <c r="R440" s="40"/>
-      <c r="U440" s="9" t="s">
+      <c r="U440" s="79" t="s">
         <v>1774</v>
       </c>
-      <c r="V440" s="9" t="s">
+      <c r="V440" s="79" t="s">
         <v>1771</v>
       </c>
     </row>
@@ -27112,10 +27409,10 @@
       <c r="P441" s="40"/>
       <c r="Q441" s="40"/>
       <c r="R441" s="40"/>
-      <c r="U441" s="9" t="s">
+      <c r="U441" s="79" t="s">
         <v>1775</v>
       </c>
-      <c r="V441" s="9" t="s">
+      <c r="V441" s="79" t="s">
         <v>1776</v>
       </c>
     </row>
@@ -27159,10 +27456,10 @@
       <c r="P442" s="40"/>
       <c r="Q442" s="40"/>
       <c r="R442" s="40"/>
-      <c r="U442" s="9" t="s">
+      <c r="U442" s="79" t="s">
         <v>1777</v>
       </c>
-      <c r="V442" s="9" t="s">
+      <c r="V442" s="79" t="s">
         <v>1776</v>
       </c>
     </row>
@@ -27206,10 +27503,10 @@
       <c r="P443" s="40"/>
       <c r="Q443" s="40"/>
       <c r="R443" s="40"/>
-      <c r="U443" s="9" t="s">
+      <c r="U443" s="79" t="s">
         <v>1778</v>
       </c>
-      <c r="V443" s="9" t="s">
+      <c r="V443" s="79" t="s">
         <v>1779</v>
       </c>
     </row>
@@ -27253,10 +27550,10 @@
       <c r="P444" s="40"/>
       <c r="Q444" s="40"/>
       <c r="R444" s="40"/>
-      <c r="U444" s="9" t="s">
+      <c r="U444" s="79" t="s">
         <v>1780</v>
       </c>
-      <c r="V444" s="9" t="s">
+      <c r="V444" s="79" t="s">
         <v>1779</v>
       </c>
     </row>
@@ -27300,10 +27597,10 @@
       <c r="P445" s="40"/>
       <c r="Q445" s="40"/>
       <c r="R445" s="40"/>
-      <c r="U445" s="9" t="s">
+      <c r="U445" s="79" t="s">
         <v>1781</v>
       </c>
-      <c r="V445" s="9" t="s">
+      <c r="V445" s="79" t="s">
         <v>1779</v>
       </c>
     </row>
@@ -27347,10 +27644,10 @@
       <c r="P446" s="40"/>
       <c r="Q446" s="40"/>
       <c r="R446" s="40"/>
-      <c r="U446" s="9" t="s">
+      <c r="U446" s="79" t="s">
         <v>1782</v>
       </c>
-      <c r="V446" s="9" t="s">
+      <c r="V446" s="79" t="s">
         <v>1783</v>
       </c>
     </row>
@@ -27394,10 +27691,10 @@
       <c r="P447" s="40"/>
       <c r="Q447" s="40"/>
       <c r="R447" s="40"/>
-      <c r="U447" s="9" t="s">
+      <c r="U447" s="79" t="s">
         <v>1784</v>
       </c>
-      <c r="V447" s="9" t="s">
+      <c r="V447" s="79" t="s">
         <v>1783</v>
       </c>
     </row>
@@ -27441,10 +27738,10 @@
       <c r="P448" s="40"/>
       <c r="Q448" s="40"/>
       <c r="R448" s="40"/>
-      <c r="U448" s="9" t="s">
+      <c r="U448" s="79" t="s">
         <v>1785</v>
       </c>
-      <c r="V448" s="9" t="s">
+      <c r="V448" s="79" t="s">
         <v>1786</v>
       </c>
     </row>
@@ -27488,10 +27785,10 @@
       <c r="P449" s="40"/>
       <c r="Q449" s="40"/>
       <c r="R449" s="40"/>
-      <c r="U449" s="9" t="s">
+      <c r="U449" s="79" t="s">
         <v>1787</v>
       </c>
-      <c r="V449" s="9" t="s">
+      <c r="V449" s="79" t="s">
         <v>1786</v>
       </c>
     </row>
@@ -27535,10 +27832,10 @@
       <c r="P450" s="40"/>
       <c r="Q450" s="40"/>
       <c r="R450" s="40"/>
-      <c r="U450" s="9" t="s">
+      <c r="U450" s="79" t="s">
         <v>1788</v>
       </c>
-      <c r="V450" s="9" t="s">
+      <c r="V450" s="79" t="s">
         <v>1786</v>
       </c>
     </row>
@@ -27582,10 +27879,10 @@
       <c r="P451" s="40"/>
       <c r="Q451" s="40"/>
       <c r="R451" s="40"/>
-      <c r="U451" s="9" t="s">
+      <c r="U451" s="79" t="s">
         <v>1789</v>
       </c>
-      <c r="V451" s="9" t="s">
+      <c r="V451" s="79" t="s">
         <v>1790</v>
       </c>
     </row>
@@ -27629,10 +27926,10 @@
       <c r="P452" s="40"/>
       <c r="Q452" s="40"/>
       <c r="R452" s="40"/>
-      <c r="U452" s="9" t="s">
+      <c r="U452" s="79" t="s">
         <v>1791</v>
       </c>
-      <c r="V452" s="9" t="s">
+      <c r="V452" s="79" t="s">
         <v>1790</v>
       </c>
     </row>
@@ -27676,10 +27973,10 @@
       <c r="P453" s="40"/>
       <c r="Q453" s="40"/>
       <c r="R453" s="40"/>
-      <c r="U453" s="9" t="s">
+      <c r="U453" s="79" t="s">
         <v>1792</v>
       </c>
-      <c r="V453" s="9" t="s">
+      <c r="V453" s="79" t="s">
         <v>1790</v>
       </c>
     </row>
@@ -27723,10 +28020,10 @@
       <c r="P454" s="40"/>
       <c r="Q454" s="40"/>
       <c r="R454" s="40"/>
-      <c r="U454" s="9" t="s">
+      <c r="U454" s="79" t="s">
         <v>1793</v>
       </c>
-      <c r="V454" s="9" t="s">
+      <c r="V454" s="79" t="s">
         <v>1790</v>
       </c>
     </row>
@@ -27773,8 +28070,12 @@
       <c r="S455" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U455" s="10"/>
-      <c r="V455" s="10"/>
+      <c r="U455" s="80" t="s">
+        <v>1932</v>
+      </c>
+      <c r="V455" s="80" t="s">
+        <v>1931</v>
+      </c>
     </row>
     <row r="456" spans="1:22" ht="30" customHeight="1">
       <c r="A456" s="43" t="s">
@@ -27819,8 +28120,12 @@
       <c r="S456" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U456" s="10"/>
-      <c r="V456" s="10"/>
+      <c r="U456" s="80" t="s">
+        <v>1934</v>
+      </c>
+      <c r="V456" s="80" t="s">
+        <v>1934</v>
+      </c>
     </row>
     <row r="457" spans="1:22" ht="30" customHeight="1">
       <c r="A457" s="43" t="s">
@@ -27865,8 +28170,12 @@
       <c r="S457" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U457" s="10"/>
-      <c r="V457" s="10"/>
+      <c r="U457" s="83" t="s">
+        <v>1907</v>
+      </c>
+      <c r="V457" s="83" t="s">
+        <v>1698</v>
+      </c>
     </row>
     <row r="458" spans="1:22" ht="30" customHeight="1">
       <c r="A458" s="43" t="s">
@@ -27911,8 +28220,12 @@
       <c r="S458" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U458" s="10"/>
-      <c r="V458" s="10"/>
+      <c r="U458" s="83" t="s">
+        <v>1908</v>
+      </c>
+      <c r="V458" s="83" t="s">
+        <v>1702</v>
+      </c>
     </row>
     <row r="459" spans="1:22" ht="30" customHeight="1">
       <c r="A459" s="43" t="s">
@@ -27957,8 +28270,12 @@
       <c r="S459" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U459" s="10"/>
-      <c r="V459" s="10"/>
+      <c r="U459" s="83" t="s">
+        <v>1909</v>
+      </c>
+      <c r="V459" s="83" t="s">
+        <v>1713</v>
+      </c>
     </row>
     <row r="460" spans="1:22" ht="30" customHeight="1">
       <c r="A460" s="43" t="s">
@@ -28003,8 +28320,12 @@
       <c r="S460" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U460" s="10"/>
-      <c r="V460" s="10"/>
+      <c r="U460" s="83" t="s">
+        <v>1910</v>
+      </c>
+      <c r="V460" s="83" t="s">
+        <v>1738</v>
+      </c>
     </row>
     <row r="461" spans="1:22" ht="30" customHeight="1">
       <c r="A461" s="43" t="s">
@@ -28049,8 +28370,12 @@
       <c r="S461" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U461" s="10"/>
-      <c r="V461" s="10"/>
+      <c r="U461" s="83" t="s">
+        <v>1911</v>
+      </c>
+      <c r="V461" s="83" t="s">
+        <v>1768</v>
+      </c>
     </row>
     <row r="462" spans="1:22" ht="30" customHeight="1">
       <c r="A462" s="43" t="s">
@@ -28095,8 +28420,12 @@
       <c r="S462" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U462" s="10"/>
-      <c r="V462" s="10"/>
+      <c r="U462" s="80" t="s">
+        <v>1935</v>
+      </c>
+      <c r="V462" s="80" t="s">
+        <v>1779</v>
+      </c>
     </row>
     <row r="463" spans="1:22" ht="30" customHeight="1">
       <c r="A463" s="43" t="s">
@@ -28141,8 +28470,12 @@
       <c r="S463" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U463" s="10"/>
-      <c r="V463" s="10"/>
+      <c r="U463" s="83" t="s">
+        <v>1912</v>
+      </c>
+      <c r="V463" s="83" t="s">
+        <v>1786</v>
+      </c>
     </row>
     <row r="464" spans="1:22" ht="30" customHeight="1">
       <c r="A464" s="43" t="s">
@@ -28187,8 +28520,12 @@
       <c r="S464" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U464" s="10"/>
-      <c r="V464" s="10"/>
+      <c r="U464" s="80" t="s">
+        <v>1936</v>
+      </c>
+      <c r="V464" s="80" t="s">
+        <v>1931</v>
+      </c>
     </row>
     <row r="465" spans="1:22" ht="30" customHeight="1">
       <c r="A465" s="43" t="s">
@@ -28233,8 +28570,12 @@
       <c r="S465" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U465" s="10"/>
-      <c r="V465" s="10"/>
+      <c r="U465" s="80" t="s">
+        <v>1937</v>
+      </c>
+      <c r="V465" s="80" t="s">
+        <v>1931</v>
+      </c>
     </row>
     <row r="466" spans="1:22" ht="30" customHeight="1">
       <c r="A466" s="43" t="s">
@@ -28279,8 +28620,12 @@
       <c r="S466" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U466" s="10"/>
-      <c r="V466" s="10"/>
+      <c r="U466" s="80" t="s">
+        <v>1938</v>
+      </c>
+      <c r="V466" s="80" t="s">
+        <v>1931</v>
+      </c>
     </row>
     <row r="467" spans="1:22" ht="15" customHeight="1">
       <c r="A467" s="43"/>
@@ -28302,8 +28647,8 @@
       <c r="Q467" s="40"/>
       <c r="R467" s="40"/>
       <c r="S467" s="39"/>
-      <c r="U467" s="10"/>
-      <c r="V467" s="10"/>
+      <c r="U467" s="81"/>
+      <c r="V467" s="81"/>
     </row>
     <row r="468" spans="1:22" ht="30" customHeight="1">
       <c r="A468" s="43"/>
@@ -28342,10 +28687,10 @@
       <c r="P468" s="40"/>
       <c r="Q468" s="40"/>
       <c r="R468" s="40"/>
-      <c r="U468" s="9" t="s">
+      <c r="U468" s="79" t="s">
         <v>1794</v>
       </c>
-      <c r="V468" s="9" t="s">
+      <c r="V468" s="79" t="s">
         <v>1795</v>
       </c>
     </row>
@@ -28389,10 +28734,10 @@
       <c r="P469" s="40"/>
       <c r="Q469" s="40"/>
       <c r="R469" s="40"/>
-      <c r="U469" s="9" t="s">
+      <c r="U469" s="79" t="s">
         <v>1796</v>
       </c>
-      <c r="V469" s="9" t="s">
+      <c r="V469" s="79" t="s">
         <v>1795</v>
       </c>
     </row>
@@ -28436,10 +28781,10 @@
       <c r="P470" s="40"/>
       <c r="Q470" s="40"/>
       <c r="R470" s="40"/>
-      <c r="U470" s="9" t="s">
+      <c r="U470" s="79" t="s">
         <v>1797</v>
       </c>
-      <c r="V470" s="9" t="s">
+      <c r="V470" s="79" t="s">
         <v>1798</v>
       </c>
     </row>
@@ -28483,10 +28828,10 @@
       <c r="P471" s="40"/>
       <c r="Q471" s="40"/>
       <c r="R471" s="40"/>
-      <c r="U471" s="9" t="s">
+      <c r="U471" s="79" t="s">
         <v>1799</v>
       </c>
-      <c r="V471" s="9" t="s">
+      <c r="V471" s="79" t="s">
         <v>1798</v>
       </c>
     </row>
@@ -28530,10 +28875,10 @@
       <c r="P472" s="40"/>
       <c r="Q472" s="40"/>
       <c r="R472" s="40"/>
-      <c r="U472" s="9" t="s">
+      <c r="U472" s="79" t="s">
         <v>1800</v>
       </c>
-      <c r="V472" s="9" t="s">
+      <c r="V472" s="79" t="s">
         <v>1798</v>
       </c>
     </row>
@@ -28577,10 +28922,10 @@
       <c r="P473" s="40"/>
       <c r="Q473" s="40"/>
       <c r="R473" s="40"/>
-      <c r="U473" s="9" t="s">
+      <c r="U473" s="79" t="s">
         <v>1801</v>
       </c>
-      <c r="V473" s="9" t="s">
+      <c r="V473" s="79" t="s">
         <v>1798</v>
       </c>
     </row>
@@ -28624,10 +28969,10 @@
       <c r="P474" s="40"/>
       <c r="Q474" s="40"/>
       <c r="R474" s="40"/>
-      <c r="U474" s="9" t="s">
+      <c r="U474" s="79" t="s">
         <v>1802</v>
       </c>
-      <c r="V474" s="9" t="s">
+      <c r="V474" s="79" t="s">
         <v>1798</v>
       </c>
     </row>
@@ -28671,10 +29016,10 @@
       <c r="P475" s="40"/>
       <c r="Q475" s="40"/>
       <c r="R475" s="40"/>
-      <c r="U475" s="9" t="s">
+      <c r="U475" s="79" t="s">
         <v>1803</v>
       </c>
-      <c r="V475" s="9" t="s">
+      <c r="V475" s="79" t="s">
         <v>1804</v>
       </c>
     </row>
@@ -28718,10 +29063,10 @@
       <c r="P476" s="40"/>
       <c r="Q476" s="40"/>
       <c r="R476" s="40"/>
-      <c r="U476" s="9" t="s">
+      <c r="U476" s="79" t="s">
         <v>1805</v>
       </c>
-      <c r="V476" s="9" t="s">
+      <c r="V476" s="79" t="s">
         <v>1804</v>
       </c>
     </row>
@@ -28765,10 +29110,10 @@
       <c r="P477" s="40"/>
       <c r="Q477" s="40"/>
       <c r="R477" s="40"/>
-      <c r="U477" s="9" t="s">
+      <c r="U477" s="79" t="s">
         <v>1806</v>
       </c>
-      <c r="V477" s="9" t="s">
+      <c r="V477" s="79" t="s">
         <v>1807</v>
       </c>
     </row>
@@ -28812,10 +29157,10 @@
       <c r="P478" s="40"/>
       <c r="Q478" s="40"/>
       <c r="R478" s="40"/>
-      <c r="U478" s="9" t="s">
+      <c r="U478" s="79" t="s">
         <v>1808</v>
       </c>
-      <c r="V478" s="9" t="s">
+      <c r="V478" s="79" t="s">
         <v>1809</v>
       </c>
     </row>
@@ -28859,10 +29204,10 @@
       <c r="P479" s="40"/>
       <c r="Q479" s="40"/>
       <c r="R479" s="40"/>
-      <c r="U479" s="9" t="s">
+      <c r="U479" s="79" t="s">
         <v>1810</v>
       </c>
-      <c r="V479" s="9" t="s">
+      <c r="V479" s="79" t="s">
         <v>1809</v>
       </c>
     </row>
@@ -28906,10 +29251,10 @@
       <c r="P480" s="40"/>
       <c r="Q480" s="40"/>
       <c r="R480" s="40"/>
-      <c r="U480" s="9" t="s">
+      <c r="U480" s="79" t="s">
         <v>1811</v>
       </c>
-      <c r="V480" s="9" t="s">
+      <c r="V480" s="79" t="s">
         <v>1809</v>
       </c>
     </row>
@@ -28953,10 +29298,10 @@
       <c r="P481" s="40"/>
       <c r="Q481" s="40"/>
       <c r="R481" s="40"/>
-      <c r="U481" s="9" t="s">
+      <c r="U481" s="79" t="s">
         <v>1812</v>
       </c>
-      <c r="V481" s="9" t="s">
+      <c r="V481" s="79" t="s">
         <v>1813</v>
       </c>
     </row>
@@ -29000,10 +29345,10 @@
       <c r="P482" s="40"/>
       <c r="Q482" s="40"/>
       <c r="R482" s="40"/>
-      <c r="U482" s="9" t="s">
+      <c r="U482" s="79" t="s">
         <v>1814</v>
       </c>
-      <c r="V482" s="9" t="s">
+      <c r="V482" s="79" t="s">
         <v>1813</v>
       </c>
     </row>
@@ -29047,10 +29392,10 @@
       <c r="P483" s="40"/>
       <c r="Q483" s="40"/>
       <c r="R483" s="40"/>
-      <c r="U483" s="9" t="s">
+      <c r="U483" s="79" t="s">
         <v>1815</v>
       </c>
-      <c r="V483" s="9" t="s">
+      <c r="V483" s="79" t="s">
         <v>1813</v>
       </c>
     </row>
@@ -29097,8 +29442,12 @@
       <c r="S484" s="39" t="s">
         <v>1887</v>
       </c>
-      <c r="U484" s="10"/>
-      <c r="V484" s="10"/>
+      <c r="U484" s="80" t="s">
+        <v>1939</v>
+      </c>
+      <c r="V484" s="80" t="s">
+        <v>1940</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="18">
